--- a/HasilTrucking.xlsx
+++ b/HasilTrucking.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A85ADF-8E22-4829-BBBA-4F4FF8A5A3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HASIL_ANALISA" sheetId="1" r:id="rId1"/>

--- a/HasilTrucking.xlsx
+++ b/HasilTrucking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\SPIL\bbm\Analisa BBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A85ADF-8E22-4829-BBBA-4F4FF8A5A3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED25E9BA-40EB-4456-89AA-4FDB2CB7B229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,21 +18,20 @@
     <sheet name="Laporan_Tren" sheetId="3" r:id="rId3"/>
     <sheet name="OPS_TANPA_BBM" sheetId="4" r:id="rId4"/>
     <sheet name="BBM_TANPA_OPS" sheetId="5" r:id="rId5"/>
-    <sheet name="GAGAL_MAPPING" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">BBM_TANPA_OPS!$A$1:$C$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">BBM_TANPA_OPS!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data_Bulanan!$A$1:$G$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HASIL_ANALISA!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Laporan_Tren!$A$1:$D$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">OPS_TANPA_BBM!$A$1:$E$2</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="99">
   <si>
     <t>Nama_Unit</t>
   </si>
@@ -61,39 +60,21 @@
     <t>L 8047 UQ</t>
   </si>
   <si>
-    <t>L 8060 UR (EX.L 9200 UN)</t>
-  </si>
-  <si>
     <t>L 8191 US</t>
   </si>
   <si>
-    <t>L 8208 UK (EX.L 9436 US)</t>
-  </si>
-  <si>
-    <t>L 8217 UK (EX.L 9069 UT)</t>
-  </si>
-  <si>
     <t>L 8246 US</t>
   </si>
   <si>
     <t>L 8252 US</t>
   </si>
   <si>
-    <t>L 8253 UK (EX.L 9070 UN)</t>
-  </si>
-  <si>
     <t>L 8257 US</t>
   </si>
   <si>
     <t>L 8266 US</t>
   </si>
   <si>
-    <t>L 8271 UK (EX.L 9440 US)</t>
-  </si>
-  <si>
-    <t>L 8280 UK (EX.L 9435 US)</t>
-  </si>
-  <si>
     <t>L 8295 UQ</t>
   </si>
   <si>
@@ -103,57 +84,18 @@
     <t>L 8311 UQ</t>
   </si>
   <si>
-    <t>L 8316 UK (EX.L 9070 UR)</t>
-  </si>
-  <si>
     <t>L 8322 UQ</t>
   </si>
   <si>
     <t>L 8327 UQ</t>
   </si>
   <si>
-    <t>L 8334 UK (EX.L 9437 US)</t>
-  </si>
-  <si>
-    <t>L 8460 UK (EX.L 9637 US)</t>
-  </si>
-  <si>
-    <t>L 8469 UK (EX.L 9069 US)</t>
-  </si>
-  <si>
-    <t>L 8478 UK (EX.L 9070 UQ)</t>
-  </si>
-  <si>
-    <t>L 8496 UK (EX.L 9634 US)</t>
-  </si>
-  <si>
-    <t>L 8514 UK (EX.L 9635 US)</t>
-  </si>
-  <si>
-    <t>L 8523 UK (EX.L 9636 US)</t>
-  </si>
-  <si>
-    <t>L 8568 UK (EX.L 9627 US)</t>
-  </si>
-  <si>
-    <t>L 8640 UK (EX.L 9562 UQ)</t>
-  </si>
-  <si>
-    <t>L 8649 UK (EX.L 9580 UQ)</t>
-  </si>
-  <si>
-    <t>L 8799 UO (EX.L 9300 UQ)</t>
-  </si>
-  <si>
     <t>L 8810 UQ</t>
   </si>
   <si>
     <t>L 8834 UQ</t>
   </si>
   <si>
-    <t>L 8857 UO (EX.L 9300 UR)</t>
-  </si>
-  <si>
     <t>L 8859 UQ</t>
   </si>
   <si>
@@ -166,13 +108,10 @@
     <t>L 8986 UQ</t>
   </si>
   <si>
-    <t>L 8999 UUC (EX.L 9703 UQ)</t>
-  </si>
-  <si>
-    <t>L 9041 NN (EX.L 9621 QA)</t>
-  </si>
-  <si>
-    <t>L 9054 UT (EX.L 8048 UO)</t>
+    <t>L 9041 NN</t>
+  </si>
+  <si>
+    <t>L 9054 UT</t>
   </si>
   <si>
     <t>L 9055 UN</t>
@@ -196,25 +135,85 @@
     <t>L 9067 UN</t>
   </si>
   <si>
+    <t>L 9069 US</t>
+  </si>
+  <si>
+    <t>L 9069 UT</t>
+  </si>
+  <si>
+    <t>L 9070 UN</t>
+  </si>
+  <si>
+    <t>L 9070 UQ</t>
+  </si>
+  <si>
+    <t>L 9070 UR</t>
+  </si>
+  <si>
     <t>L 9115 UQ</t>
   </si>
   <si>
     <t>L9120UQ</t>
   </si>
   <si>
-    <t>L 9201 UN (EX.L 9300 US)</t>
+    <t>L 9200 UN</t>
+  </si>
+  <si>
+    <t>L 9300 UN</t>
+  </si>
+  <si>
+    <t>L 9300 UQ</t>
+  </si>
+  <si>
+    <t>L 9300 UR</t>
+  </si>
+  <si>
+    <t>L 9300 US</t>
+  </si>
+  <si>
+    <t>L 9435 US</t>
+  </si>
+  <si>
+    <t>L 9436 US</t>
+  </si>
+  <si>
+    <t>L 9437 US</t>
+  </si>
+  <si>
+    <t>L 9439 US</t>
+  </si>
+  <si>
+    <t>L 9440 US</t>
+  </si>
+  <si>
+    <t>L 9562 UQ</t>
+  </si>
+  <si>
+    <t>L 9569 UQ</t>
+  </si>
+  <si>
+    <t>L 9580 UQ</t>
+  </si>
+  <si>
+    <t>L 9627 US</t>
+  </si>
+  <si>
+    <t>L 9634 US</t>
+  </si>
+  <si>
+    <t>L 9635 US</t>
+  </si>
+  <si>
+    <t>L 9636 US</t>
+  </si>
+  <si>
+    <t>L 9637 US</t>
   </si>
   <si>
     <t>L 9664 UQ</t>
   </si>
   <si>
-    <t>L 9668 UR (EX.L 9300 UN)</t>
-  </si>
-  <si>
-    <t>L 9844 UK (EX.L 9569 UQ)</t>
-  </si>
-  <si>
-    <t>L 9848 UK (EX.L 9439 US)</t>
+    <t>L 9703 UQ</t>
   </si>
   <si>
     <t>PA 8511 AH</t>
@@ -235,264 +234,39 @@
     <t>Status_Tren</t>
   </si>
   <si>
-    <t>MEMBAIK (Irit)</t>
-  </si>
-  <si>
-    <t>MEMBURUK (Boros)</t>
+    <t>MEMBAIK (Makin Irit)</t>
+  </si>
+  <si>
+    <t>MEMBURUK (Makin Boros)</t>
   </si>
   <si>
     <t>Keterangan</t>
   </si>
   <si>
-    <t>L8577UKEXL9561UQ</t>
+    <t>L9561UQ</t>
   </si>
   <si>
     <t>Ada Kegiatan Dooring/Haulage, Tapi Data BBM Tidak Ditemukan</t>
   </si>
   <si>
-    <t>AKASIA</t>
-  </si>
-  <si>
-    <t>ALPINE</t>
-  </si>
-  <si>
     <t>B 9225 BL</t>
   </si>
   <si>
     <t>B 9273 NK</t>
   </si>
   <si>
-    <t>BANTENG 1</t>
-  </si>
-  <si>
-    <t>BANTENG 4</t>
-  </si>
-  <si>
-    <t>BENGKIRAI</t>
-  </si>
-  <si>
-    <t>BERNARD BEAR</t>
-  </si>
-  <si>
-    <t>CAMAR</t>
-  </si>
-  <si>
-    <t>CEMARA</t>
-  </si>
-  <si>
-    <t>CENDET</t>
-  </si>
-  <si>
-    <t>CRANE LB 75/KANGGURU</t>
-  </si>
-  <si>
-    <t>CRANE LB 80T/LUCKY DOLPHIN</t>
-  </si>
-  <si>
-    <t>ELANG</t>
-  </si>
-  <si>
-    <t>FLAMINGO</t>
-  </si>
-  <si>
-    <t>FL RENTAL 01</t>
-  </si>
-  <si>
-    <t>FORKLIF MITS/KENANGA</t>
-  </si>
-  <si>
-    <t>GAJAH TUNGGAL</t>
-  </si>
-  <si>
-    <t>GARUDA</t>
-  </si>
-  <si>
-    <t>GATUT KACA</t>
-  </si>
-  <si>
-    <t>GENSET DP BALIKPAPAN</t>
-  </si>
-  <si>
-    <t>GENSET DP SAMARINDA</t>
-  </si>
-  <si>
-    <t>GENSET HVE 01 TIMIKA</t>
-  </si>
-  <si>
-    <t>GENSET KUPP NABIRE</t>
-  </si>
-  <si>
-    <t>GENSET MEKANIK 01 CAB JAKARTA</t>
-  </si>
-  <si>
-    <t>GENSET OFFICE DP BAYUR</t>
-  </si>
-  <si>
-    <t>GENSET OFFICE DP JPF</t>
-  </si>
-  <si>
-    <t>GENSET OFFICE DP LANGON</t>
-  </si>
-  <si>
-    <t>GENSET OFFICE DP YONIF</t>
-  </si>
-  <si>
-    <t>GENSET REEFER DP BAYUR</t>
-  </si>
-  <si>
-    <t>GIANT</t>
-  </si>
-  <si>
-    <t>GLATIK</t>
-  </si>
-  <si>
-    <t>HATORI</t>
-  </si>
-  <si>
-    <t>JALAK</t>
-  </si>
-  <si>
-    <t>JATAYU</t>
-  </si>
-  <si>
-    <t>KAKATUA</t>
-  </si>
-  <si>
-    <t>KALAMR5/KINGKONG 1</t>
-  </si>
-  <si>
-    <t>KALMAR11/KINGKONG 2</t>
-  </si>
-  <si>
-    <t>KALMAR 12</t>
-  </si>
-  <si>
-    <t>KALMAR 13</t>
-  </si>
-  <si>
-    <t>KALMAR 14</t>
-  </si>
-  <si>
-    <t>KALMAR 15</t>
-  </si>
-  <si>
-    <t>KALMAR 16</t>
-  </si>
-  <si>
-    <t>KALMAR 17</t>
-  </si>
-  <si>
-    <t>KALMAR 18</t>
-  </si>
-  <si>
-    <t>KALMAR 19</t>
-  </si>
-  <si>
-    <t>KALMAR1/GAJAH</t>
-  </si>
-  <si>
-    <t>KALMAR 20</t>
-  </si>
-  <si>
-    <t>KALMAR 21</t>
-  </si>
-  <si>
-    <t>KALMAR 22</t>
-  </si>
-  <si>
-    <t>KALMAR 23</t>
-  </si>
-  <si>
-    <t>KALMAR 24</t>
-  </si>
-  <si>
-    <t>KALMAR 25</t>
-  </si>
-  <si>
-    <t>KALMAR 26</t>
-  </si>
-  <si>
-    <t>KALMAR 27</t>
-  </si>
-  <si>
-    <t>KALMAR 28</t>
-  </si>
-  <si>
-    <t>KALMAR 29</t>
-  </si>
-  <si>
-    <t>KALMAR2/BISON</t>
-  </si>
-  <si>
-    <t>KALMAR 30</t>
-  </si>
-  <si>
-    <t>KALMAR 31</t>
-  </si>
-  <si>
-    <t>KALMAR 32</t>
-  </si>
-  <si>
-    <t>KALMAR 4</t>
-  </si>
-  <si>
-    <t>KALMAR 7</t>
-  </si>
-  <si>
-    <t>KALONG</t>
-  </si>
-  <si>
-    <t>KAMBOJA</t>
-  </si>
-  <si>
-    <t>KANTIL</t>
-  </si>
-  <si>
-    <t>KASUARI</t>
-  </si>
-  <si>
-    <t>KENARI</t>
-  </si>
-  <si>
-    <t>KOLIBRI</t>
-  </si>
-  <si>
-    <t>KOMPRESSOR BAN CAB BALIKPAPAN</t>
-  </si>
-  <si>
-    <t>KOMPRESSOR BAN CAB TUAL</t>
-  </si>
-  <si>
-    <t>KONECRANES</t>
-  </si>
-  <si>
-    <t>KONECRANES 2</t>
-  </si>
-  <si>
-    <t>KONECRANES 3</t>
-  </si>
-  <si>
-    <t>KUDA PUTIH</t>
-  </si>
-  <si>
-    <t>KUTILANG</t>
-  </si>
-  <si>
-    <t>L 8073 UL (EX.L 8341 UR)</t>
+    <t>L 8084 NQ</t>
   </si>
   <si>
     <t>L 8251 UO</t>
   </si>
   <si>
+    <t>L 8341 UR</t>
+  </si>
+  <si>
     <t>L 8408 UO</t>
   </si>
   <si>
-    <t>L 8487 UK (EX.L 9631 US)</t>
-  </si>
-  <si>
-    <t>L 8595 UK (EX.L 9624 US)</t>
-  </si>
-  <si>
     <t>L 8604 UK (EX.L 9620 US)</t>
   </si>
   <si>
@@ -502,28 +276,13 @@
     <t>L 8613 UK (EX.L 9566 UQ)</t>
   </si>
   <si>
-    <t>L 8622 UK (EX.L 9626 US)</t>
-  </si>
-  <si>
     <t>L 8625 US</t>
   </si>
   <si>
     <t>L 8625 UT</t>
   </si>
   <si>
-    <t>L 8631 UK (EX.L 9623 US)</t>
-  </si>
-  <si>
-    <t>L 8658 UK (EX.L 9582 UQ)</t>
-  </si>
-  <si>
-    <t>L 8676 UK (EX.L 9581 UQ)</t>
-  </si>
-  <si>
-    <t>L 8703 UK (EX.L 9173 UQ)</t>
-  </si>
-  <si>
-    <t>L 8796 UO (EX.L 9025 US)</t>
+    <t>L 9025 US</t>
   </si>
   <si>
     <t>L 9049 UQ</t>
@@ -538,157 +297,37 @@
     <t>L 9098 UA (EX.L 9690 UO)</t>
   </si>
   <si>
+    <t>L 9173 UQ</t>
+  </si>
+  <si>
+    <t>L 9581 UQ</t>
+  </si>
+  <si>
+    <t>L9582UQ</t>
+  </si>
+  <si>
     <t>L 9622 US</t>
   </si>
   <si>
+    <t>L 9623 US</t>
+  </si>
+  <si>
+    <t>L 9624 US</t>
+  </si>
+  <si>
+    <t>L 9626 US</t>
+  </si>
+  <si>
+    <t>L 9631 US</t>
+  </si>
+  <si>
     <t>L 9633 US</t>
   </si>
   <si>
     <t>L 9743 UR</t>
   </si>
   <si>
-    <t>L 9968 CQ (EX.L 8084 NQ)</t>
-  </si>
-  <si>
-    <t>LINDE</t>
-  </si>
-  <si>
-    <t>MAGNETO</t>
-  </si>
-  <si>
-    <t>MATAHARI</t>
-  </si>
-  <si>
-    <t>MERAK</t>
-  </si>
-  <si>
-    <t>MERPATI</t>
-  </si>
-  <si>
-    <t>MESIN LAS REPAIR CONT BYR</t>
-  </si>
-  <si>
-    <t>MESIN LAS REPAIR CONT JPF</t>
-  </si>
-  <si>
-    <t>MOBIL SOLAR LOGISTIC EMC</t>
-  </si>
-  <si>
-    <t>MOBIL STOORING MEKANIK TRAILER</t>
-  </si>
-  <si>
-    <t>MOBIL STORING MEKANIK EMC</t>
-  </si>
-  <si>
-    <t>PADI</t>
-  </si>
-  <si>
-    <t>PENYU</t>
-  </si>
-  <si>
-    <t>PERKUTUT</t>
-  </si>
-  <si>
-    <t>PINUS</t>
-  </si>
-  <si>
-    <t>PRENJAK</t>
-  </si>
-  <si>
-    <t>RAFLESIA</t>
-  </si>
-  <si>
-    <t>RANDU</t>
-  </si>
-  <si>
-    <t>RANGER</t>
-  </si>
-  <si>
-    <t>RG01</t>
-  </si>
-  <si>
-    <t>RG02</t>
-  </si>
-  <si>
-    <t>RG03</t>
-  </si>
-  <si>
-    <t>ROBIN</t>
-  </si>
-  <si>
-    <t>SADEWA</t>
-  </si>
-  <si>
-    <t>SANY KUPP</t>
-  </si>
-  <si>
-    <t>SCORPION</t>
-  </si>
-  <si>
-    <t>SEMPATI</t>
-  </si>
-  <si>
-    <t>SERUNI</t>
-  </si>
-  <si>
-    <t>SIDE LOADER 3</t>
-  </si>
-  <si>
-    <t>SIDE LOADER 5T</t>
-  </si>
-  <si>
-    <t>SIDE LOADER BOSS 2</t>
-  </si>
-  <si>
-    <t>SIDE LOADER BOSS 3</t>
-  </si>
-  <si>
-    <t>SIDE LOUDER KALMAR</t>
-  </si>
-  <si>
-    <t>SMV</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>TOP LOADER MITS 42T/BADAK</t>
-  </si>
-  <si>
-    <t>TREMBESI</t>
-  </si>
-  <si>
-    <t>TULIB</t>
-  </si>
-  <si>
-    <t>TYRANOSAURUS</t>
-  </si>
-  <si>
-    <t>ULIN</t>
-  </si>
-  <si>
-    <t>WALET</t>
-  </si>
-  <si>
-    <t>WARLOCK</t>
-  </si>
-  <si>
-    <t>WERKUDORO</t>
-  </si>
-  <si>
-    <t>WIND RIVER (EX.TL BOSS 42T)</t>
-  </si>
-  <si>
-    <t>WINDU</t>
-  </si>
-  <si>
-    <t>XAVIER</t>
-  </si>
-  <si>
-    <t>Ada Pengisian BBM, Tapi Tidak Ada Kegiatan Dooring/Haulage (Unit Idle/Rusak/Lainnya)</t>
-  </si>
-  <si>
-    <t>Kode_Lambung</t>
+    <t>Ada Pengisian BBM, Tapi Tidak Ada Kegiatan Dooring/Haulage (Truk Sedang Idle/Standby)</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +698,7 @@
   <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
@@ -1096,22 +735,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>22370.213500000002</v>
+        <v>7595.2631000000001</v>
       </c>
       <c r="C2">
-        <v>4214.8999999999996</v>
+        <v>4225.3999999999996</v>
       </c>
       <c r="D2">
-        <v>449820.12878499989</v>
+        <v>137749.16516999999</v>
       </c>
       <c r="E2">
-        <v>7383.88</v>
+        <v>3686.05</v>
       </c>
       <c r="F2">
-        <v>1.6415183597818201E-2</v>
+        <v>2.6759145839112309E-2</v>
       </c>
       <c r="G2">
-        <v>3.0296014426019919</v>
+        <v>2.060542613366612</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1119,22 +758,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>5875.4</v>
+        <v>4362.0200000000004</v>
       </c>
       <c r="C3">
-        <v>27567.1</v>
+        <v>28073.4</v>
       </c>
       <c r="D3">
-        <v>126535.67999999999</v>
+        <v>93446.717499999999</v>
       </c>
       <c r="E3">
-        <v>6445.91</v>
+        <v>3218.22</v>
       </c>
       <c r="F3">
-        <v>5.0941441971149963E-2</v>
+        <v>3.4439090918308608E-2</v>
       </c>
       <c r="G3">
-        <v>0.91149271398452658</v>
+        <v>1.355413862321408</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,22 +781,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>8996.2808000000005</v>
+        <v>8423.0128999999997</v>
       </c>
       <c r="C4">
-        <v>14541.7</v>
+        <v>7268.7000000000007</v>
       </c>
       <c r="D4">
-        <v>168407.904595</v>
+        <v>175554.51056</v>
       </c>
       <c r="E4">
-        <v>7331.93</v>
+        <v>4878.5299999999988</v>
       </c>
       <c r="F4">
-        <v>4.3536733133948652E-2</v>
+        <v>2.778926035245698E-2</v>
       </c>
       <c r="G4">
-        <v>1.2270003668883911</v>
+        <v>1.726547320606822</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1165,22 +804,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>29091.6266</v>
+        <v>7737.4874999999993</v>
       </c>
       <c r="C5">
-        <v>7175.3</v>
+        <v>3668.4</v>
       </c>
       <c r="D5">
-        <v>663322.69725999993</v>
+        <v>150621.293535</v>
       </c>
       <c r="E5">
-        <v>9770.9700000000012</v>
+        <v>3889.89</v>
       </c>
       <c r="F5">
-        <v>1.473034171808252E-2</v>
+        <v>2.5825631348041129E-2</v>
       </c>
       <c r="G5">
-        <v>2.9773529751907941</v>
+        <v>1.9891275845846541</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1188,22 +827,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>5951.5999999999995</v>
+        <v>9424.8538000000008</v>
       </c>
       <c r="C6">
-        <v>21572.799999999999</v>
+        <v>12573.4</v>
       </c>
       <c r="D6">
-        <v>113985.5</v>
+        <v>190110.21562</v>
       </c>
       <c r="E6">
-        <v>7645.8</v>
+        <v>5284.09</v>
       </c>
       <c r="F6">
-        <v>6.7076952770308507E-2</v>
+        <v>2.7794876686490399E-2</v>
       </c>
       <c r="G6">
-        <v>0.77841429281435548</v>
+        <v>1.7836285528823319</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1211,22 +850,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>7731.1208999999999</v>
+        <v>7522.3388999999997</v>
       </c>
       <c r="C7">
-        <v>15682.4</v>
+        <v>5544.2000000000007</v>
       </c>
       <c r="D7">
-        <v>143952.50349500001</v>
+        <v>152436.610865</v>
       </c>
       <c r="E7">
-        <v>5473.22</v>
+        <v>4369.42</v>
       </c>
       <c r="F7">
-        <v>3.8021012952998798E-2</v>
+        <v>2.8663849026856279E-2</v>
       </c>
       <c r="G7">
-        <v>1.4125361121972071</v>
+        <v>1.721587510470497</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1234,22 +873,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>17017.346099999999</v>
+        <v>6614.1414999999997</v>
       </c>
       <c r="C8">
-        <v>3668.4</v>
+        <v>4321.5</v>
       </c>
       <c r="D8">
-        <v>320386.30493500002</v>
+        <v>127453.73241500001</v>
       </c>
       <c r="E8">
-        <v>7791.7900000000009</v>
+        <v>3968.87</v>
       </c>
       <c r="F8">
-        <v>2.4319984593538731E-2</v>
+        <v>3.1139692222406069E-2</v>
       </c>
       <c r="G8">
-        <v>2.1840098488280608</v>
+        <v>1.6665049497715969</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1257,22 +896,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>17095.213100000001</v>
+        <v>5713.3579</v>
       </c>
       <c r="C9">
-        <v>12400</v>
+        <v>3553.6</v>
       </c>
       <c r="D9">
-        <v>322987.21325999999</v>
+        <v>110935.5294</v>
       </c>
       <c r="E9">
-        <v>10582.58</v>
+        <v>3985.17</v>
       </c>
       <c r="F9">
-        <v>3.2764702643138931E-2</v>
+        <v>3.5923297266024487E-2</v>
       </c>
       <c r="G9">
-        <v>1.6154107126995501</v>
+        <v>1.433654749985571</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1280,22 +919,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>3467.6</v>
+        <v>8627.3831000000009</v>
       </c>
       <c r="C10">
-        <v>16323.9</v>
+        <v>3049.4</v>
       </c>
       <c r="D10">
-        <v>54579.44</v>
+        <v>128969.92461</v>
       </c>
       <c r="E10">
-        <v>5992.57</v>
+        <v>4042.63</v>
       </c>
       <c r="F10">
-        <v>0.10979537349595379</v>
+        <v>3.1345525030155343E-2</v>
       </c>
       <c r="G10">
-        <v>0.57864989478637718</v>
+        <v>2.1341015873329989</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1303,22 +942,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>26238.715800000002</v>
+        <v>6653.2226999999993</v>
       </c>
       <c r="C11">
-        <v>5508.2000000000007</v>
+        <v>4169.3</v>
       </c>
       <c r="D11">
-        <v>582619.5539099999</v>
+        <v>149519.032175</v>
       </c>
       <c r="E11">
-        <v>8751.1899999999987</v>
+        <v>4135.8</v>
       </c>
       <c r="F11">
-        <v>1.5020419313547169E-2</v>
+        <v>2.7660692688000942E-2</v>
       </c>
       <c r="G11">
-        <v>2.9983026079881721</v>
+        <v>1.6086906281735089</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1326,22 +965,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>20312.787899999999</v>
+        <v>8927.5493999999999</v>
       </c>
       <c r="C12">
-        <v>4314</v>
+        <v>3468.7</v>
       </c>
       <c r="D12">
-        <v>405940.85019000003</v>
+        <v>130704.960935</v>
       </c>
       <c r="E12">
-        <v>7951.0599999999986</v>
+        <v>4724.7</v>
       </c>
       <c r="F12">
-        <v>1.9586745202604072E-2</v>
+        <v>3.6147824582952209E-2</v>
       </c>
       <c r="G12">
-        <v>2.5547270301066778</v>
+        <v>1.88954841577243</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1349,22 +988,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>4748.6120000000001</v>
+        <v>5690.5442999999996</v>
       </c>
       <c r="C13">
-        <v>21328.3</v>
+        <v>3781.1</v>
       </c>
       <c r="D13">
-        <v>85681.854955000003</v>
+        <v>103568.72255000001</v>
       </c>
       <c r="E13">
-        <v>7149.8600000000006</v>
+        <v>4324.2299999999996</v>
       </c>
       <c r="F13">
-        <v>8.344660609594759E-2</v>
+        <v>4.1752277072958831E-2</v>
       </c>
       <c r="G13">
-        <v>0.66415454288615439</v>
+        <v>1.3159670739067999</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1372,22 +1011,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>3690.7946999999999</v>
+        <v>4697.0034999999998</v>
       </c>
       <c r="C14">
-        <v>15125.4</v>
+        <v>2995</v>
       </c>
       <c r="D14">
-        <v>63152.332354999999</v>
+        <v>91970.07815500001</v>
       </c>
       <c r="E14">
-        <v>6108.65</v>
+        <v>3058.66</v>
       </c>
       <c r="F14">
-        <v>9.6728810674184956E-2</v>
+        <v>3.3257120808847712E-2</v>
       </c>
       <c r="G14">
-        <v>0.60419154805071495</v>
+        <v>1.5356409342653321</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1395,22 +1034,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>20068.572499999998</v>
+        <v>7281.1396000000004</v>
       </c>
       <c r="C15">
-        <v>3538.6</v>
+        <v>4797.8</v>
       </c>
       <c r="D15">
-        <v>413145.24064999999</v>
+        <v>156424.22844499999</v>
       </c>
       <c r="E15">
-        <v>7983.09</v>
+        <v>4345.9400000000014</v>
       </c>
       <c r="F15">
-        <v>1.9322720473410829E-2</v>
+        <v>2.778303619076547E-2</v>
       </c>
       <c r="G15">
-        <v>2.513885287526509</v>
+        <v>1.6753888917012201</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1418,22 +1057,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>14878.174800000001</v>
+        <v>7357.0729000000001</v>
       </c>
       <c r="C16">
-        <v>3047.9</v>
+        <v>3231.2</v>
       </c>
       <c r="D16">
-        <v>221823.45726</v>
+        <v>119107.919135</v>
       </c>
       <c r="E16">
-        <v>8096.85</v>
+        <v>4157.7899999999991</v>
       </c>
       <c r="F16">
-        <v>3.6501324521823031E-2</v>
+        <v>3.4907754498569088E-2</v>
       </c>
       <c r="G16">
-        <v>1.8375262972637501</v>
+        <v>1.769467168856532</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1441,22 +1080,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>20096.210999999999</v>
+        <v>8422.9611999999997</v>
       </c>
       <c r="C17">
-        <v>4158.8</v>
+        <v>3244.2</v>
       </c>
       <c r="D17">
-        <v>417049.78011499997</v>
+        <v>134664.34411999999</v>
       </c>
       <c r="E17">
-        <v>8287.01</v>
+        <v>3941.01</v>
       </c>
       <c r="F17">
-        <v>1.9870553576877292E-2</v>
+        <v>2.9265430472732629E-2</v>
       </c>
       <c r="G17">
-        <v>2.4250255520386719</v>
+        <v>2.1372595349922991</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1464,22 +1103,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>4342.2</v>
+        <v>4425.5034999999998</v>
       </c>
       <c r="C18">
-        <v>25420.5</v>
+        <v>2943.4</v>
       </c>
       <c r="D18">
-        <v>80372.179999999993</v>
+        <v>64696.079449999997</v>
       </c>
       <c r="E18">
-        <v>6951.6</v>
+        <v>2141.19</v>
       </c>
       <c r="F18">
-        <v>8.6492614733107917E-2</v>
+        <v>3.3096132226293658E-2</v>
       </c>
       <c r="G18">
-        <v>0.62463317797341611</v>
+        <v>2.066842970497714</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1487,22 +1126,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>17462.339199999999</v>
+        <v>4780.3</v>
       </c>
       <c r="C19">
-        <v>3468.7</v>
+        <v>18200.3</v>
       </c>
       <c r="D19">
-        <v>256919.48160500001</v>
+        <v>82502.92</v>
       </c>
       <c r="E19">
-        <v>9465.2900000000009</v>
+        <v>3268.84</v>
       </c>
       <c r="F19">
-        <v>3.684146465215269E-2</v>
+        <v>3.962090069054526E-2</v>
       </c>
       <c r="G19">
-        <v>1.844881583131631</v>
+        <v>1.462384209689064</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1510,22 +1149,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>17225.514299999999</v>
+        <v>1758.54</v>
       </c>
       <c r="C20">
-        <v>3752.6</v>
+        <v>10404.9</v>
       </c>
       <c r="D20">
-        <v>309168.57196500001</v>
+        <v>33647.8125</v>
       </c>
       <c r="E20">
-        <v>8661.1</v>
+        <v>2171.0700000000002</v>
       </c>
       <c r="F20">
-        <v>2.8014166980014049E-2</v>
+        <v>6.4523362402830783E-2</v>
       </c>
       <c r="G20">
-        <v>1.9888367874750319</v>
+        <v>0.80998770191656655</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1533,22 +1172,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>5776.1306999999997</v>
+        <v>2633.0722999999998</v>
       </c>
       <c r="C21">
-        <v>22997.3</v>
+        <v>22034</v>
       </c>
       <c r="D21">
-        <v>135594.43757499999</v>
+        <v>51115.686170000001</v>
       </c>
       <c r="E21">
-        <v>6770.1</v>
+        <v>3170.67</v>
       </c>
       <c r="F21">
-        <v>4.9929039281241337E-2</v>
+        <v>6.202929545844342E-2</v>
       </c>
       <c r="G21">
-        <v>0.85318247884078513</v>
+        <v>0.83044665638492821</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1556,22 +1195,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>5755.9121999999998</v>
+        <v>5830.0700000000006</v>
       </c>
       <c r="C22">
-        <v>24269.1</v>
+        <v>29847.599999999999</v>
       </c>
       <c r="D22">
-        <v>114051.36192</v>
+        <v>123360.6125</v>
       </c>
       <c r="E22">
-        <v>6707.99</v>
+        <v>3795.86</v>
       </c>
       <c r="F22">
-        <v>5.8815518614369913E-2</v>
+        <v>3.0770437363060271E-2</v>
       </c>
       <c r="G22">
-        <v>0.85806809491367753</v>
+        <v>1.5359022724758029</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1579,22 +1218,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>3287.5165999999999</v>
+        <v>5811.7782999999999</v>
       </c>
       <c r="C23">
-        <v>16266.2</v>
+        <v>37618.399999999987</v>
       </c>
       <c r="D23">
-        <v>58907.416380000002</v>
+        <v>129302.61334500001</v>
       </c>
       <c r="E23">
-        <v>6143.07</v>
+        <v>4057.12</v>
       </c>
       <c r="F23">
-        <v>0.10428347358458701</v>
+        <v>3.1376937364560112E-2</v>
       </c>
       <c r="G23">
-        <v>0.53515857706325987</v>
+        <v>1.4324886372599279</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1602,22 +1241,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>5919</v>
+        <v>3170.4027999999998</v>
       </c>
       <c r="C24">
-        <v>19488.3</v>
+        <v>26332.1</v>
       </c>
       <c r="D24">
-        <v>121616.92</v>
+        <v>59550.560019999997</v>
       </c>
       <c r="E24">
-        <v>7213.47</v>
+        <v>3386.31</v>
       </c>
       <c r="F24">
-        <v>5.9313046243894357E-2</v>
+        <v>5.6864452640961079E-2</v>
       </c>
       <c r="G24">
-        <v>0.82054822436358643</v>
+        <v>0.9362411592559452</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1625,22 +1264,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>5138.0610999999999</v>
+        <v>6874.4660000000003</v>
       </c>
       <c r="C25">
-        <v>25084.5</v>
+        <v>18684.400000000001</v>
       </c>
       <c r="D25">
-        <v>104093.277875</v>
+        <v>143034.767445</v>
       </c>
       <c r="E25">
-        <v>5524.7000000000007</v>
+        <v>3763.24</v>
       </c>
       <c r="F25">
-        <v>5.3074512713821097E-2</v>
+        <v>2.630996692078412E-2</v>
       </c>
       <c r="G25">
-        <v>0.93001630857784123</v>
+        <v>1.82674131865095</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1648,22 +1287,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>7413.7916999999998</v>
+        <v>3273.73</v>
       </c>
       <c r="C26">
-        <v>21285.5</v>
+        <v>29208.7</v>
       </c>
       <c r="D26">
-        <v>152798.32358500001</v>
+        <v>63515.7575</v>
       </c>
       <c r="E26">
-        <v>6938.08</v>
+        <v>3691.33</v>
       </c>
       <c r="F26">
-        <v>4.5406780894035291E-2</v>
+        <v>5.8116759451384947E-2</v>
       </c>
       <c r="G26">
-        <v>1.068565323547725</v>
+        <v>0.88687004413043535</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1671,22 +1310,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>6421</v>
+        <v>4790.0749999999998</v>
       </c>
       <c r="C27">
-        <v>17453.2</v>
+        <v>21778.6</v>
       </c>
       <c r="D27">
-        <v>119387.62</v>
+        <v>84291.38</v>
       </c>
       <c r="E27">
-        <v>7647.51</v>
+        <v>3286.77</v>
       </c>
       <c r="F27">
-        <v>6.4056139154126709E-2</v>
+        <v>3.89929551515232E-2</v>
       </c>
       <c r="G27">
-        <v>0.83961969320733154</v>
+        <v>1.457380650304098</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1694,22 +1333,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>16028.950199999999</v>
+        <v>2633.49</v>
       </c>
       <c r="C28">
-        <v>3104.1</v>
+        <v>19118</v>
       </c>
       <c r="D28">
-        <v>234031.25042999999</v>
+        <v>39328.684999999998</v>
       </c>
       <c r="E28">
-        <v>5780.24</v>
+        <v>2669.94</v>
       </c>
       <c r="F28">
-        <v>2.4698581874769331E-2</v>
+        <v>6.7887853356907307E-2</v>
       </c>
       <c r="G28">
-        <v>2.7730596307419759</v>
+        <v>0.98634800782040055</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1717,22 +1356,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>3945</v>
+        <v>2458.1028000000001</v>
       </c>
       <c r="C29">
-        <v>22491.3</v>
+        <v>16654.5</v>
       </c>
       <c r="D29">
-        <v>69860.2</v>
+        <v>46078.565540000003</v>
       </c>
       <c r="E29">
-        <v>7068.84</v>
+        <v>3066.83</v>
       </c>
       <c r="F29">
-        <v>0.1011855104909519</v>
+        <v>6.655654237625383E-2</v>
       </c>
       <c r="G29">
-        <v>0.55808308010932484</v>
+        <v>0.80151257161303369</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1740,22 +1379,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>6374.2</v>
+        <v>4961.3446999999996</v>
       </c>
       <c r="C30">
-        <v>25931.8</v>
+        <v>15785.9</v>
       </c>
       <c r="D30">
-        <v>126601.06</v>
+        <v>99844.088760000013</v>
       </c>
       <c r="E30">
-        <v>8015.73</v>
+        <v>2732.05</v>
       </c>
       <c r="F30">
-        <v>6.3314872719075183E-2</v>
+        <v>2.736316224556026E-2</v>
       </c>
       <c r="G30">
-        <v>0.79521141555416652</v>
+        <v>1.815978733917754</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1763,22 +1402,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>6919.4242999999997</v>
+        <v>2635.13</v>
       </c>
       <c r="C31">
-        <v>18196.2</v>
+        <v>15941.6</v>
       </c>
       <c r="D31">
-        <v>120677.27647</v>
+        <v>38715.769999999997</v>
       </c>
       <c r="E31">
-        <v>6966.34</v>
+        <v>2992.49</v>
       </c>
       <c r="F31">
-        <v>5.7727023709652679E-2</v>
+        <v>7.7293826262528148E-2</v>
       </c>
       <c r="G31">
-        <v>0.99326537320888719</v>
+        <v>0.88058105457328184</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1786,22 +1425,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>10981.112800000001</v>
+        <v>5792.4750000000004</v>
       </c>
       <c r="C32">
-        <v>2963.2</v>
+        <v>20219.900000000001</v>
       </c>
       <c r="D32">
-        <v>230111.15228499999</v>
+        <v>126419.8575</v>
       </c>
       <c r="E32">
-        <v>6133.51</v>
+        <v>3602.08</v>
       </c>
       <c r="F32">
-        <v>2.6654553415140229E-2</v>
+        <v>2.8492992091847601E-2</v>
       </c>
       <c r="G32">
-        <v>1.7903472563018561</v>
+        <v>1.608091713676542</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1809,22 +1448,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>23871.037</v>
+        <v>3102.07</v>
       </c>
       <c r="C33">
-        <v>4791.8</v>
+        <v>25334.2</v>
       </c>
       <c r="D33">
-        <v>550983.39736499987</v>
+        <v>56474.445</v>
       </c>
       <c r="E33">
-        <v>8703.82</v>
+        <v>3446.6</v>
       </c>
       <c r="F33">
-        <v>1.579688252245855E-2</v>
+        <v>6.1029373551169913E-2</v>
       </c>
       <c r="G33">
-        <v>2.7425931372661658</v>
+        <v>0.90003771833110902</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1832,22 +1471,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>10271.504199999999</v>
+        <v>2289.3449999999998</v>
       </c>
       <c r="C34">
-        <v>14676.9</v>
+        <v>16706.8</v>
       </c>
       <c r="D34">
-        <v>193981.03841000001</v>
+        <v>36907.824999999997</v>
       </c>
       <c r="E34">
-        <v>7573.67</v>
+        <v>2795.9</v>
       </c>
       <c r="F34">
-        <v>3.9043352185754499E-2</v>
+        <v>7.575358342031803E-2</v>
       </c>
       <c r="G34">
-        <v>1.356212272253742</v>
+        <v>0.81882220394148597</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1855,22 +1494,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>14454.843699999999</v>
+        <v>2991.5956000000001</v>
       </c>
       <c r="C35">
-        <v>3223.7</v>
+        <v>18789.099999999999</v>
       </c>
       <c r="D35">
-        <v>238323.59573999999</v>
+        <v>53459.142809999998</v>
       </c>
       <c r="E35">
-        <v>8327.84</v>
+        <v>3088.02</v>
       </c>
       <c r="F35">
-        <v>3.4943413698261282E-2</v>
+        <v>5.7764113633007187E-2</v>
       </c>
       <c r="G35">
-        <v>1.7357254342062289</v>
+        <v>0.96877468410178713</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1878,22 +1517,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>16441.547299999998</v>
+        <v>6068.5943000000007</v>
       </c>
       <c r="C36">
-        <v>3239.7</v>
+        <v>14685.5</v>
       </c>
       <c r="D36">
-        <v>282313.88318499998</v>
+        <v>127185.85691</v>
       </c>
       <c r="E36">
-        <v>7895.62</v>
+        <v>3661.13</v>
       </c>
       <c r="F36">
-        <v>2.7967522924921159E-2</v>
+        <v>2.8785669169101951E-2</v>
       </c>
       <c r="G36">
-        <v>2.082363044320775</v>
+        <v>1.657574109632818</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1901,22 +1540,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>17576.167399999998</v>
+        <v>3404.0535</v>
       </c>
       <c r="C37">
-        <v>2943.4</v>
+        <v>23974.9</v>
       </c>
       <c r="D37">
-        <v>258532.99025999999</v>
+        <v>58589.656850000007</v>
       </c>
       <c r="E37">
-        <v>4289.869999999999</v>
+        <v>3428.33</v>
       </c>
       <c r="F37">
-        <v>1.659312413354206E-2</v>
+        <v>5.8514252929952083E-2</v>
       </c>
       <c r="G37">
-        <v>4.0971328734903398</v>
+        <v>0.99291885553607739</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1924,22 +1563,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>5448.2</v>
+        <v>5021.8432000000003</v>
       </c>
       <c r="C38">
-        <v>17568.2</v>
+        <v>18472.599999999999</v>
       </c>
       <c r="D38">
-        <v>89417.02</v>
+        <v>91332.570030000003</v>
       </c>
       <c r="E38">
-        <v>6545.3099999999986</v>
+        <v>3479.08</v>
       </c>
       <c r="F38">
-        <v>7.3199822584112048E-2</v>
+        <v>3.809243513959179E-2</v>
       </c>
       <c r="G38">
-        <v>0.83238227066403281</v>
+        <v>1.4434399898823831</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1947,22 +1586,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>18915.9607</v>
+        <v>7828.2888000000003</v>
       </c>
       <c r="C39">
-        <v>3497.8</v>
+        <v>14994.2</v>
       </c>
       <c r="D39">
-        <v>380827.02410999988</v>
+        <v>169929.60068500001</v>
       </c>
       <c r="E39">
-        <v>7567.05</v>
+        <v>3782.16</v>
       </c>
       <c r="F39">
-        <v>1.9870044720918481E-2</v>
+        <v>2.2257217016657518E-2</v>
       </c>
       <c r="G39">
-        <v>2.4997800596005049</v>
+        <v>2.0697931340821119</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1970,22 +1609,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>2345</v>
+        <v>10782.757799999999</v>
       </c>
       <c r="C40">
-        <v>10579.2</v>
+        <v>23193.8</v>
       </c>
       <c r="D40">
-        <v>45876.800000000003</v>
+        <v>231178.83347000001</v>
       </c>
       <c r="E40">
-        <v>4350.6399999999994</v>
+        <v>4276.74</v>
       </c>
       <c r="F40">
-        <v>9.4833118264569458E-2</v>
+        <v>1.8499704042130621E-2</v>
       </c>
       <c r="G40">
-        <v>0.53900115845025109</v>
+        <v>2.5212563307566049</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,22 +1632,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>3617.7946999999999</v>
+        <v>3138.7728000000002</v>
       </c>
       <c r="C41">
-        <v>21597.4</v>
+        <v>15744.9</v>
       </c>
       <c r="D41">
-        <v>69909.12513</v>
+        <v>57623.939769999997</v>
       </c>
       <c r="E41">
-        <v>6346.1900000000014</v>
+        <v>3050.09</v>
       </c>
       <c r="F41">
-        <v>9.077770588887929E-2</v>
+        <v>5.2930952173248121E-2</v>
       </c>
       <c r="G41">
-        <v>0.57007349291464637</v>
+        <v>1.0290754699041671</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2016,22 +1655,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>6942</v>
+        <v>5394.66</v>
       </c>
       <c r="C42">
-        <v>28696.6</v>
+        <v>22357.8</v>
       </c>
       <c r="D42">
-        <v>141699.48000000001</v>
+        <v>111021.9</v>
       </c>
       <c r="E42">
-        <v>7599.2599999999993</v>
+        <v>3818.58</v>
       </c>
       <c r="F42">
-        <v>5.3629413460091743E-2</v>
+        <v>3.4394835613514092E-2</v>
       </c>
       <c r="G42">
-        <v>0.9135099996578615</v>
+        <v>1.4127398142765111</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2039,22 +1678,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>7615.4400999999998</v>
+        <v>5184.9047</v>
       </c>
       <c r="C43">
-        <v>36381.899999999987</v>
+        <v>23725.3</v>
       </c>
       <c r="D43">
-        <v>161796.11746499999</v>
+        <v>129924.61689</v>
       </c>
       <c r="E43">
-        <v>8121.8200000000024</v>
+        <v>3380.73</v>
       </c>
       <c r="F43">
-        <v>5.0197867088849817E-2</v>
+        <v>2.6020704012252559E-2</v>
       </c>
       <c r="G43">
-        <v>0.9376519179198749</v>
+        <v>1.533664238197076</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,22 +1701,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>4401.9893999999986</v>
+        <v>4674.2129999999997</v>
       </c>
       <c r="C44">
-        <v>25715.200000000001</v>
+        <v>10737.2</v>
       </c>
       <c r="D44">
-        <v>82238.564709999991</v>
+        <v>110719.44658</v>
       </c>
       <c r="E44">
-        <v>6781.91</v>
+        <v>3196.1</v>
       </c>
       <c r="F44">
-        <v>8.2466298188875589E-2</v>
+        <v>2.8866654401949771E-2</v>
       </c>
       <c r="G44">
-        <v>0.64907812106029117</v>
+        <v>1.462473952629767</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2085,22 +1724,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>8848.8011000000006</v>
+        <v>3797.4425999999999</v>
       </c>
       <c r="C45">
-        <v>18474.5</v>
+        <v>21621.5</v>
       </c>
       <c r="D45">
-        <v>169441.56138</v>
+        <v>72037.399980000017</v>
       </c>
       <c r="E45">
-        <v>7536.62</v>
+        <v>3570.84</v>
       </c>
       <c r="F45">
-        <v>4.4479169919226097E-2</v>
+        <v>4.9569251541440762E-2</v>
       </c>
       <c r="G45">
-        <v>1.174107371739586</v>
+        <v>1.0634591860738649</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2108,22 +1747,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>4715.5999999999995</v>
+        <v>2944.86</v>
       </c>
       <c r="C46">
-        <v>28453.7</v>
+        <v>23106.400000000001</v>
       </c>
       <c r="D46">
-        <v>91264.14</v>
+        <v>52291.707499999997</v>
       </c>
       <c r="E46">
-        <v>7389.8099999999986</v>
+        <v>3530.29</v>
       </c>
       <c r="F46">
-        <v>8.0971671896541184E-2</v>
+        <v>6.7511469194231219E-2</v>
       </c>
       <c r="G46">
-        <v>0.63812195442102027</v>
+        <v>0.83416943083995931</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2131,22 +1770,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>5338.4</v>
+        <v>6125.0706</v>
       </c>
       <c r="C47">
-        <v>21208.7</v>
+        <v>23698.5</v>
       </c>
       <c r="D47">
-        <v>94351.48</v>
+        <v>126086.61857999999</v>
       </c>
       <c r="E47">
-        <v>6581.59</v>
+        <v>3897.35</v>
       </c>
       <c r="F47">
-        <v>6.9756086497000366E-2</v>
+        <v>3.091010008748226E-2</v>
       </c>
       <c r="G47">
-        <v>0.81111099293635724</v>
+        <v>1.5715988043157529</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2154,22 +1793,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>3665.8</v>
+        <v>5496.85</v>
       </c>
       <c r="C48">
-        <v>18613.2</v>
+        <v>25981.4</v>
       </c>
       <c r="D48">
-        <v>57554.7</v>
+        <v>115297.705</v>
       </c>
       <c r="E48">
-        <v>5348.99</v>
+        <v>4003.58</v>
       </c>
       <c r="F48">
-        <v>9.2937501194515826E-2</v>
+        <v>3.4723848145980007E-2</v>
       </c>
       <c r="G48">
-        <v>0.68532564091538772</v>
+        <v>1.372983679606752</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2177,22 +1816,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>3248.8</v>
+        <v>5379.3707000000004</v>
       </c>
       <c r="C49">
-        <v>16278.4</v>
+        <v>3104.1</v>
       </c>
       <c r="D49">
-        <v>51932.24</v>
+        <v>77990.828255</v>
       </c>
       <c r="E49">
-        <v>5599.49</v>
+        <v>2884.04</v>
       </c>
       <c r="F49">
-        <v>0.1078230016652469</v>
+        <v>3.6979220050982142E-2</v>
       </c>
       <c r="G49">
-        <v>0.58019569639377866</v>
+        <v>1.865220558660768</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2200,22 +1839,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>3856.7112999999999</v>
+        <v>4219.6926000000003</v>
       </c>
       <c r="C50">
-        <v>18301.2</v>
+        <v>25650.400000000001</v>
       </c>
       <c r="D50">
-        <v>65667.788734999995</v>
+        <v>89737.693420000025</v>
       </c>
       <c r="E50">
-        <v>6183.66</v>
+        <v>2755.51</v>
       </c>
       <c r="F50">
-        <v>9.4165802124903858E-2</v>
+        <v>3.0706271745846701E-2</v>
       </c>
       <c r="G50">
-        <v>0.62369394500991326</v>
+        <v>1.531365373379157</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2223,22 +1862,22 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>12209.228800000001</v>
+        <v>5769.3757000000014</v>
       </c>
       <c r="C51">
-        <v>21945.1</v>
+        <v>21701.599999999999</v>
       </c>
       <c r="D51">
-        <v>238836.59977</v>
+        <v>131220.17921999999</v>
       </c>
       <c r="E51">
-        <v>8562.130000000001</v>
+        <v>3465.08</v>
       </c>
       <c r="F51">
-        <v>3.5849321285955943E-2</v>
+        <v>2.6406609262364631E-2</v>
       </c>
       <c r="G51">
-        <v>1.425956952300421</v>
+        <v>1.665005050388447</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2246,22 +1885,22 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>14664.388000000001</v>
+        <v>7503.4650000000001</v>
       </c>
       <c r="C52">
-        <v>3241.6</v>
+        <v>17858.2</v>
       </c>
       <c r="D52">
-        <v>267442.416325</v>
+        <v>135821.13250000001</v>
       </c>
       <c r="E52">
-        <v>6943.71</v>
+        <v>3817</v>
       </c>
       <c r="F52">
-        <v>2.59633834281616E-2</v>
+        <v>2.8103137779387902E-2</v>
       </c>
       <c r="G52">
-        <v>2.1118952260391062</v>
+        <v>1.9658016767094579</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2269,22 +1908,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>5874.7529999999988</v>
+        <v>4352.1175999999996</v>
       </c>
       <c r="C53">
-        <v>23461.5</v>
+        <v>24218.6</v>
       </c>
       <c r="D53">
-        <v>101781.86592500001</v>
+        <v>89298.997110000011</v>
       </c>
       <c r="E53">
-        <v>6864.4500000000007</v>
+        <v>3350.0700000000011</v>
       </c>
       <c r="F53">
-        <v>6.7442760432965612E-2</v>
+        <v>3.7515202952092819E-2</v>
       </c>
       <c r="G53">
-        <v>0.85582282630072304</v>
+        <v>1.2991124364565509</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2292,22 +1931,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>6725.6332000000002</v>
+        <v>6150.1214999999993</v>
       </c>
       <c r="C54">
-        <v>23276.6</v>
+        <v>3253.6</v>
       </c>
       <c r="D54">
-        <v>137125.87276</v>
+        <v>108695.63552500001</v>
       </c>
       <c r="E54">
-        <v>7804.12</v>
+        <v>3465.67</v>
       </c>
       <c r="F54">
-        <v>5.6912089913614627E-2</v>
+        <v>3.188416888369814E-2</v>
       </c>
       <c r="G54">
-        <v>0.86180545660497276</v>
+        <v>1.774583702429833</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2315,22 +1954,22 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>6948.6129999999994</v>
+        <v>6422.8627999999999</v>
       </c>
       <c r="C55">
-        <v>10591.1</v>
+        <v>3508.3</v>
       </c>
       <c r="D55">
-        <v>143728.22081</v>
+        <v>112876.81168</v>
       </c>
       <c r="E55">
-        <v>6400.3</v>
+        <v>3776.47</v>
       </c>
       <c r="F55">
-        <v>4.4530572798648978E-2</v>
+        <v>3.3456561571796523E-2</v>
       </c>
       <c r="G55">
-        <v>1.085669890473884</v>
+        <v>1.700758327220923</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2338,22 +1977,22 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>14625.960300000001</v>
+        <v>5310.7122000000008</v>
       </c>
       <c r="C56">
         <v>3077.1</v>
       </c>
       <c r="D56">
-        <v>213307.01839499999</v>
+        <v>76978.497479999991</v>
       </c>
       <c r="E56">
-        <v>5846.04</v>
+        <v>2918.2199999999989</v>
       </c>
       <c r="F56">
-        <v>2.740669315050083E-2</v>
+        <v>3.7909547413005701E-2</v>
       </c>
       <c r="G56">
-        <v>2.5018577190713711</v>
+        <v>1.8198464132245</v>
       </c>
     </row>
   </sheetData>
@@ -2367,7 +2006,7 @@
   <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2407,19 +2046,19 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>3243.84</v>
+        <v>1619.05</v>
       </c>
       <c r="D2">
-        <v>2222.4</v>
+        <v>2228.4</v>
       </c>
       <c r="E2">
-        <v>256537.90325999999</v>
+        <v>73953.731270000004</v>
       </c>
       <c r="F2">
-        <v>1.264468119049209E-2</v>
+        <v>2.189274255938432E-2</v>
       </c>
       <c r="G2">
-        <v>11487.3487</v>
+        <v>3553.0484999999999</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2430,19 +2069,19 @@
         <v>65</v>
       </c>
       <c r="C3">
-        <v>4140.04</v>
+        <v>2067</v>
       </c>
       <c r="D3">
-        <v>1992.5</v>
+        <v>1997</v>
       </c>
       <c r="E3">
-        <v>193282.22552499999</v>
+        <v>63795.433900000004</v>
       </c>
       <c r="F3">
-        <v>2.141966230342535E-2</v>
+        <v>3.2400437988086173E-2</v>
       </c>
       <c r="G3">
-        <v>10882.864799999999</v>
+        <v>4042.2145999999998</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2453,19 +2092,19 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>3061.24</v>
+        <v>1528.23</v>
       </c>
       <c r="D4">
-        <v>13956.5</v>
+        <v>14200.1</v>
       </c>
       <c r="E4">
-        <v>71502.22</v>
+        <v>54045.775000000001</v>
       </c>
       <c r="F4">
-        <v>4.2813216149093003E-2</v>
+        <v>2.827658591258984E-2</v>
       </c>
       <c r="G4">
-        <v>3346.6</v>
+        <v>2583.5250000000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2476,19 +2115,19 @@
         <v>65</v>
       </c>
       <c r="C5">
-        <v>3384.67</v>
+        <v>1689.99</v>
       </c>
       <c r="D5">
-        <v>13610.6</v>
+        <v>13873.3</v>
       </c>
       <c r="E5">
-        <v>55033.46</v>
+        <v>39400.942499999997</v>
       </c>
       <c r="F5">
-        <v>6.1502038941400369E-2</v>
+        <v>4.2892121171974509E-2</v>
       </c>
       <c r="G5">
-        <v>2528.8000000000002</v>
+        <v>1778.4949999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2499,19 +2138,19 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>3464.2</v>
+        <v>2400.0500000000002</v>
       </c>
       <c r="D6">
-        <v>9099.5</v>
+        <v>3947.6</v>
       </c>
       <c r="E6">
-        <v>84730.699499999988</v>
+        <v>102554.7257</v>
       </c>
       <c r="F6">
-        <v>4.0884827110391077E-2</v>
+        <v>2.3402627071723522E-2</v>
       </c>
       <c r="G6">
-        <v>4155.3552</v>
+        <v>4669.9958999999999</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2522,19 +2161,19 @@
         <v>65</v>
       </c>
       <c r="C7">
-        <v>3867.73</v>
+        <v>2478.48</v>
       </c>
       <c r="D7">
-        <v>5442.2</v>
+        <v>3321.1</v>
       </c>
       <c r="E7">
-        <v>83677.205094999998</v>
+        <v>72999.78486</v>
       </c>
       <c r="F7">
-        <v>4.6222026603408989E-2</v>
+        <v>3.3951880882296608E-2</v>
       </c>
       <c r="G7">
-        <v>4840.9255999999996</v>
+        <v>3753.0169999999998</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2545,19 +2184,19 @@
         <v>64</v>
       </c>
       <c r="C8">
-        <v>4806.59</v>
+        <v>1659.37</v>
       </c>
       <c r="D8">
-        <v>3927.2</v>
+        <v>1880</v>
       </c>
       <c r="E8">
-        <v>340985.58815000003</v>
+        <v>76117.607785</v>
       </c>
       <c r="F8">
-        <v>1.4096167600742039E-2</v>
+        <v>2.180008079979362E-2</v>
       </c>
       <c r="G8">
-        <v>14601.284900000001</v>
+        <v>3844.3669</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2568,19 +2207,19 @@
         <v>65</v>
       </c>
       <c r="C9">
-        <v>4964.380000000001</v>
+        <v>2230.52</v>
       </c>
       <c r="D9">
-        <v>3248.1</v>
+        <v>1788.4</v>
       </c>
       <c r="E9">
-        <v>322337.10911000002</v>
+        <v>74503.68574999999</v>
       </c>
       <c r="F9">
-        <v>1.5401205321059911E-2</v>
+        <v>2.9938384625488149E-2</v>
       </c>
       <c r="G9">
-        <v>14490.341700000001</v>
+        <v>3893.1206000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2591,19 +2230,19 @@
         <v>64</v>
       </c>
       <c r="C10">
-        <v>3654.940000000001</v>
+        <v>2441.4499999999998</v>
       </c>
       <c r="D10">
-        <v>12086.7</v>
+        <v>5836.6</v>
       </c>
       <c r="E10">
-        <v>55438.22</v>
+        <v>84992.448700000008</v>
       </c>
       <c r="F10">
-        <v>6.5928162917207669E-2</v>
+        <v>2.8725493115484269E-2</v>
       </c>
       <c r="G10">
-        <v>2885.2</v>
+        <v>4329.9804000000004</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2614,19 +2253,19 @@
         <v>65</v>
       </c>
       <c r="C11">
-        <v>3990.86</v>
+        <v>2842.64</v>
       </c>
       <c r="D11">
-        <v>9486.1</v>
+        <v>6736.7999999999993</v>
       </c>
       <c r="E11">
-        <v>58547.28</v>
+        <v>105117.76691999999</v>
       </c>
       <c r="F11">
-        <v>6.8164737969039713E-2</v>
+        <v>2.704243139186352E-2</v>
       </c>
       <c r="G11">
-        <v>3066.4</v>
+        <v>5094.8734000000004</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2637,19 +2276,19 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>3269.16</v>
+        <v>2085.9299999999998</v>
       </c>
       <c r="D12">
-        <v>9231</v>
+        <v>3107.8</v>
       </c>
       <c r="E12">
-        <v>102756.389725</v>
+        <v>86200.693859999999</v>
       </c>
       <c r="F12">
-        <v>3.1814663873935563E-2</v>
+        <v>2.4198529113788739E-2</v>
       </c>
       <c r="G12">
-        <v>5377.0916999999999</v>
+        <v>3951.5216</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2660,19 +2299,19 @@
         <v>65</v>
       </c>
       <c r="C13">
-        <v>2204.06</v>
+        <v>2283.4899999999998</v>
       </c>
       <c r="D13">
-        <v>6451.4000000000005</v>
+        <v>2436.4</v>
       </c>
       <c r="E13">
-        <v>41196.113770000004</v>
+        <v>66235.917004999996</v>
       </c>
       <c r="F13">
-        <v>5.350164853668915E-2</v>
+        <v>3.4475102078342548E-2</v>
       </c>
       <c r="G13">
-        <v>2354.0291999999999</v>
+        <v>3570.8173000000002</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2683,19 +2322,19 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>3323.78</v>
+        <v>1802.6</v>
       </c>
       <c r="D14">
-        <v>1880</v>
+        <v>2442.6999999999998</v>
       </c>
       <c r="E14">
-        <v>158718.91482500001</v>
+        <v>69151.382174999992</v>
       </c>
       <c r="F14">
-        <v>2.09412974103605E-2</v>
+        <v>2.6067447147161821E-2</v>
       </c>
       <c r="G14">
-        <v>8226.7075999999997</v>
+        <v>3229.6608999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2706,19 +2345,19 @@
         <v>65</v>
       </c>
       <c r="C15">
-        <v>4468.01</v>
+        <v>2166.27</v>
       </c>
       <c r="D15">
-        <v>1788.4</v>
+        <v>1878.8</v>
       </c>
       <c r="E15">
-        <v>161667.39011000001</v>
+        <v>58302.35024</v>
       </c>
       <c r="F15">
-        <v>2.7637051584490389E-2</v>
+        <v>3.7155792023522378E-2</v>
       </c>
       <c r="G15">
-        <v>8790.6384999999991</v>
+        <v>3384.4805999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2729,19 +2368,19 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>4890.5999999999995</v>
+        <v>2075.15</v>
       </c>
       <c r="D16">
-        <v>5769.2999999999993</v>
+        <v>2265.1999999999998</v>
       </c>
       <c r="E16">
-        <v>174965.94357500001</v>
+        <v>74029.393305000005</v>
       </c>
       <c r="F16">
-        <v>2.795172534764527E-2</v>
+        <v>2.8031433290968799E-2</v>
       </c>
       <c r="G16">
-        <v>9471.7356999999993</v>
+        <v>3579.6235000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2752,19 +2391,19 @@
         <v>65</v>
       </c>
       <c r="C17">
-        <v>5691.9799999999987</v>
+        <v>1910.02</v>
       </c>
       <c r="D17">
-        <v>6630.7000000000007</v>
+        <v>1288.4000000000001</v>
       </c>
       <c r="E17">
-        <v>148021.26968500001</v>
+        <v>36906.136094999987</v>
       </c>
       <c r="F17">
-        <v>3.8453797971824889E-2</v>
+        <v>5.1753453547221051E-2</v>
       </c>
       <c r="G17">
-        <v>7623.4773999999998</v>
+        <v>2133.7343999999998</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2775,19 +2414,19 @@
         <v>64</v>
       </c>
       <c r="C18">
-        <v>2597.08</v>
+        <v>1603.88</v>
       </c>
       <c r="D18">
-        <v>7095.1</v>
+        <v>1266.8</v>
       </c>
       <c r="E18">
-        <v>24571.56</v>
+        <v>56670.70658999998</v>
       </c>
       <c r="F18">
-        <v>0.1056945509361229</v>
+        <v>2.8301746996093009E-2</v>
       </c>
       <c r="G18">
-        <v>1531.4</v>
+        <v>3876.4425999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2798,19 +2437,19 @@
         <v>65</v>
       </c>
       <c r="C19">
-        <v>3395.49</v>
+        <v>2438.75</v>
       </c>
       <c r="D19">
-        <v>9228.7999999999993</v>
+        <v>1782.6</v>
       </c>
       <c r="E19">
-        <v>30007.88</v>
+        <v>72299.218019999986</v>
       </c>
       <c r="F19">
-        <v>0.11315327840553881</v>
+        <v>3.373134684977331E-2</v>
       </c>
       <c r="G19">
-        <v>1936.2</v>
+        <v>4750.9404999999997</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2821,19 +2460,19 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>4178.34</v>
+        <v>1916.77</v>
       </c>
       <c r="D20">
-        <v>3080.8</v>
+        <v>2542.8000000000002</v>
       </c>
       <c r="E20">
-        <v>298921.25619999989</v>
+        <v>81969.766865000012</v>
       </c>
       <c r="F20">
-        <v>1.3978062494172E-2</v>
+        <v>2.3383865458063601E-2</v>
       </c>
       <c r="G20">
-        <v>12188.0882</v>
+        <v>3294.8998999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2844,19 +2483,19 @@
         <v>65</v>
       </c>
       <c r="C21">
-        <v>4572.8499999999995</v>
+        <v>2219.0300000000002</v>
       </c>
       <c r="D21">
-        <v>2427.4</v>
+        <v>1626.5</v>
       </c>
       <c r="E21">
-        <v>283698.29771000001</v>
+        <v>67549.265310000003</v>
       </c>
       <c r="F21">
-        <v>1.6118707926384611E-2</v>
+        <v>3.2850542338489268E-2</v>
       </c>
       <c r="G21">
-        <v>14050.6276</v>
+        <v>3358.3227999999999</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2867,19 +2506,19 @@
         <v>64</v>
       </c>
       <c r="C22">
-        <v>3611.9</v>
+        <v>2082.94</v>
       </c>
       <c r="D22">
-        <v>2439.6999999999998</v>
+        <v>1496.4</v>
       </c>
       <c r="E22">
-        <v>201458.68583</v>
+        <v>57225.206249999981</v>
       </c>
       <c r="F22">
-        <v>1.792873801950582E-2</v>
+        <v>3.6398995066968427E-2</v>
       </c>
       <c r="G22">
-        <v>8996.7387999999992</v>
+        <v>3902.8885</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2890,19 +2529,19 @@
         <v>65</v>
       </c>
       <c r="C23">
-        <v>4339.16</v>
+        <v>2641.76</v>
       </c>
       <c r="D23">
-        <v>1874.3</v>
+        <v>1972.3</v>
       </c>
       <c r="E23">
-        <v>204482.16436</v>
+        <v>73479.754684999964</v>
       </c>
       <c r="F23">
-        <v>2.1220237048942402E-2</v>
+        <v>3.595221583584416E-2</v>
       </c>
       <c r="G23">
-        <v>11316.0491</v>
+        <v>5024.6608999999999</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2913,19 +2552,19 @@
         <v>64</v>
       </c>
       <c r="C24">
-        <v>3261.66</v>
+        <v>2069.9499999999998</v>
       </c>
       <c r="D24">
-        <v>11349.8</v>
+        <v>1886</v>
       </c>
       <c r="E24">
-        <v>36823.712355000003</v>
+        <v>50283.833525000002</v>
       </c>
       <c r="F24">
-        <v>8.8574991259867508E-2</v>
+        <v>4.1165318053383228E-2</v>
       </c>
       <c r="G24">
-        <v>2344.7946999999999</v>
+        <v>2857.2406000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2936,19 +2575,19 @@
         <v>65</v>
       </c>
       <c r="C25">
-        <v>3888.2</v>
+        <v>2254.2800000000002</v>
       </c>
       <c r="D25">
-        <v>9978.5</v>
+        <v>1895.1</v>
       </c>
       <c r="E25">
-        <v>48858.142599999999</v>
+        <v>53284.889024999997</v>
       </c>
       <c r="F25">
-        <v>7.9581412495201981E-2</v>
+        <v>4.2306178003717818E-2</v>
       </c>
       <c r="G25">
-        <v>2403.8173000000002</v>
+        <v>2833.3036999999999</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2959,19 +2598,19 @@
         <v>64</v>
       </c>
       <c r="C26">
-        <v>3190.18</v>
+        <v>729.36</v>
       </c>
       <c r="D26">
-        <v>8492.7999999999993</v>
+        <v>983.1</v>
       </c>
       <c r="E26">
-        <v>37374.972354999998</v>
+        <v>26218.569930000009</v>
       </c>
       <c r="F26">
-        <v>8.5356049757003241E-2</v>
+        <v>2.7818450889857509E-2</v>
       </c>
       <c r="G26">
-        <v>2167.7946999999999</v>
+        <v>1371.8047999999999</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2982,19 +2621,19 @@
         <v>65</v>
       </c>
       <c r="C27">
-        <v>2918.47</v>
+        <v>2329.3000000000002</v>
       </c>
       <c r="D27">
-        <v>6632.6</v>
+        <v>2011.9</v>
       </c>
       <c r="E27">
-        <v>25777.360000000001</v>
+        <v>65751.508225000012</v>
       </c>
       <c r="F27">
-        <v>0.11321834353867111</v>
+        <v>3.5425803344756653E-2</v>
       </c>
       <c r="G27">
-        <v>1523</v>
+        <v>3325.1986999999999</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3005,19 +2644,19 @@
         <v>64</v>
       </c>
       <c r="C28">
-        <v>4156.2299999999996</v>
+        <v>1990.76</v>
       </c>
       <c r="D28">
-        <v>2256.1999999999998</v>
+        <v>2711.1</v>
       </c>
       <c r="E28">
-        <v>253507.63299499999</v>
+        <v>86531.483039999992</v>
       </c>
       <c r="F28">
-        <v>1.639489095810371E-2</v>
+        <v>2.3006193006997841E-2</v>
       </c>
       <c r="G28">
-        <v>11457.895</v>
+        <v>3648.3456999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3028,19 +2667,19 @@
         <v>65</v>
       </c>
       <c r="C29">
-        <v>3826.86</v>
+        <v>2355.1799999999998</v>
       </c>
       <c r="D29">
-        <v>1282.4000000000001</v>
+        <v>2086.6999999999998</v>
       </c>
       <c r="E29">
-        <v>159637.607655</v>
+        <v>69892.745404999994</v>
       </c>
       <c r="F29">
-        <v>2.3972170819988731E-2</v>
+        <v>3.3697059492407852E-2</v>
       </c>
       <c r="G29">
-        <v>8610.6774999999998</v>
+        <v>3632.7939000000001</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3051,19 +2690,19 @@
         <v>64</v>
       </c>
       <c r="C30">
-        <v>3213.02</v>
+        <v>1706.15</v>
       </c>
       <c r="D30">
-        <v>1266.8</v>
+        <v>1285.2</v>
       </c>
       <c r="E30">
-        <v>85540.616859999995</v>
+        <v>58364.128734999977</v>
       </c>
       <c r="F30">
-        <v>3.7561337735716682E-2</v>
+        <v>2.9232853072247631E-2</v>
       </c>
       <c r="G30">
-        <v>5849.7404000000006</v>
+        <v>4027.7779</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3074,19 +2713,19 @@
         <v>65</v>
       </c>
       <c r="C31">
-        <v>4883.83</v>
+        <v>2451.639999999999</v>
       </c>
       <c r="D31">
-        <v>1781.1</v>
+        <v>1946</v>
       </c>
       <c r="E31">
-        <v>136282.84039999999</v>
+        <v>60743.790399999991</v>
       </c>
       <c r="F31">
-        <v>3.583598628899725E-2</v>
+        <v>4.0360339449610642E-2</v>
       </c>
       <c r="G31">
-        <v>9028.4344000000001</v>
+        <v>3329.2950000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3097,19 +2736,19 @@
         <v>64</v>
       </c>
       <c r="C32">
-        <v>3841</v>
+        <v>2164.62</v>
       </c>
       <c r="D32">
-        <v>2539.8000000000002</v>
+        <v>1507.7</v>
       </c>
       <c r="E32">
-        <v>242140.48696499999</v>
+        <v>78255.794504999969</v>
       </c>
       <c r="F32">
-        <v>1.5862692142661769E-2</v>
+        <v>2.7660827082417482E-2</v>
       </c>
       <c r="G32">
-        <v>10791.0933</v>
+        <v>5338.7492000000002</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3120,19 +2759,19 @@
         <v>65</v>
       </c>
       <c r="C33">
-        <v>4446.01</v>
+        <v>1776.39</v>
       </c>
       <c r="D33">
-        <v>1619</v>
+        <v>1736.5</v>
       </c>
       <c r="E33">
-        <v>174909.29315000001</v>
+        <v>56408.549615000004</v>
       </c>
       <c r="F33">
-        <v>2.5418946700488689E-2</v>
+        <v>3.1491502832890199E-2</v>
       </c>
       <c r="G33">
-        <v>9305.1177000000007</v>
+        <v>3084.212</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3143,19 +2782,19 @@
         <v>64</v>
       </c>
       <c r="C34">
-        <v>3185.77</v>
+        <v>936.64</v>
       </c>
       <c r="D34">
-        <v>11511.1</v>
+        <v>1212.4000000000001</v>
       </c>
       <c r="E34">
-        <v>35977.46</v>
+        <v>29404.793795000001</v>
       </c>
       <c r="F34">
-        <v>8.8549052656857946E-2</v>
+        <v>3.1853309583802163E-2</v>
       </c>
       <c r="G34">
-        <v>2081</v>
+        <v>2011.1468</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3166,19 +2805,19 @@
         <v>65</v>
       </c>
       <c r="C35">
-        <v>3765.83</v>
+        <v>1204.55</v>
       </c>
       <c r="D35">
-        <v>13909.4</v>
+        <v>1731</v>
       </c>
       <c r="E35">
-        <v>44394.719999999987</v>
+        <v>35291.285655</v>
       </c>
       <c r="F35">
-        <v>8.4826078416532433E-2</v>
+        <v>3.4131655383014978E-2</v>
       </c>
       <c r="G35">
-        <v>2261.1999999999998</v>
+        <v>2414.3566999999998</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3189,19 +2828,19 @@
         <v>64</v>
       </c>
       <c r="C36">
-        <v>4173.1099999999997</v>
+        <v>1439</v>
       </c>
       <c r="D36">
-        <v>1496.4</v>
+        <v>9060.7000000000007</v>
       </c>
       <c r="E36">
-        <v>110771.07202000001</v>
+        <v>35431.402499999997</v>
       </c>
       <c r="F36">
-        <v>3.7673283501729903E-2</v>
+        <v>4.0613690073374883E-2</v>
       </c>
       <c r="G36">
-        <v>7475.0423000000001</v>
+        <v>2425.0500000000002</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3212,19 +2851,19 @@
         <v>65</v>
       </c>
       <c r="C37">
-        <v>5292.18</v>
+        <v>1829.84</v>
       </c>
       <c r="D37">
-        <v>1972.3</v>
+        <v>9139.6</v>
       </c>
       <c r="E37">
-        <v>146148.40958499999</v>
+        <v>47071.517500000002</v>
       </c>
       <c r="F37">
-        <v>3.6210999592999782E-2</v>
+        <v>3.8873613964113228E-2</v>
       </c>
       <c r="G37">
-        <v>9987.2968999999994</v>
+        <v>2355.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3235,19 +2874,19 @@
         <v>64</v>
       </c>
       <c r="C38">
-        <v>4146.01</v>
+        <v>654.28</v>
       </c>
       <c r="D38">
-        <v>1872</v>
+        <v>3300.4</v>
       </c>
       <c r="E38">
-        <v>163766.69286499999</v>
+        <v>7761.5300000000007</v>
       </c>
       <c r="F38">
-        <v>2.531656423823455E-2</v>
+        <v>8.4297812415850992E-2</v>
       </c>
       <c r="G38">
-        <v>9267.1520999999993</v>
+        <v>464.21499999999997</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3258,19 +2897,19 @@
         <v>65</v>
       </c>
       <c r="C39">
-        <v>4515.09</v>
+        <v>1516.79</v>
       </c>
       <c r="D39">
-        <v>1880.6</v>
+        <v>7104.5</v>
       </c>
       <c r="E39">
-        <v>145401.87909999999</v>
+        <v>25886.282500000001</v>
       </c>
       <c r="F39">
-        <v>3.1052487271466089E-2</v>
+        <v>5.8594353978791661E-2</v>
       </c>
       <c r="G39">
-        <v>7958.3621999999996</v>
+        <v>1294.325</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3281,19 +2920,19 @@
         <v>64</v>
       </c>
       <c r="C40">
-        <v>3664.19</v>
+        <v>1638.68</v>
       </c>
       <c r="D40">
-        <v>13314.8</v>
+        <v>11668.5</v>
       </c>
       <c r="E40">
-        <v>80567.596065000005</v>
+        <v>25826.053670000001</v>
       </c>
       <c r="F40">
-        <v>4.547969877422952E-2</v>
+        <v>6.3450654170347356E-2</v>
       </c>
       <c r="G40">
-        <v>3416.0194000000001</v>
+        <v>1339.4573</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3304,19 +2943,19 @@
         <v>65</v>
       </c>
       <c r="C41">
-        <v>3105.9100000000012</v>
+        <v>1531.99</v>
       </c>
       <c r="D41">
-        <v>9682.5</v>
+        <v>10365.5</v>
       </c>
       <c r="E41">
-        <v>55026.841509999998</v>
+        <v>25289.6325</v>
       </c>
       <c r="F41">
-        <v>5.6443544909543203E-2</v>
+        <v>6.0577788150934973E-2</v>
       </c>
       <c r="G41">
-        <v>2360.1113</v>
+        <v>1293.615</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3327,19 +2966,19 @@
         <v>64</v>
       </c>
       <c r="C42">
-        <v>2270.1</v>
+        <v>1884.36</v>
       </c>
       <c r="D42">
-        <v>8677</v>
+        <v>16599.099999999999</v>
       </c>
       <c r="E42">
-        <v>37214.959999999999</v>
+        <v>56564.875</v>
       </c>
       <c r="F42">
-        <v>6.0999662501316672E-2</v>
+        <v>3.3313253145171799E-2</v>
       </c>
       <c r="G42">
-        <v>1772.8</v>
+        <v>2658.9650000000001</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3350,19 +2989,19 @@
         <v>65</v>
       </c>
       <c r="C43">
-        <v>4437.8900000000003</v>
+        <v>1911.5</v>
       </c>
       <c r="D43">
-        <v>15592.1</v>
+        <v>13248.5</v>
       </c>
       <c r="E43">
-        <v>76836.401920000004</v>
+        <v>66795.737500000003</v>
       </c>
       <c r="F43">
-        <v>5.7757649878251882E-2</v>
+        <v>2.8617095514515429E-2</v>
       </c>
       <c r="G43">
-        <v>3983.1122</v>
+        <v>3171.105</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3373,19 +3012,19 @@
         <v>64</v>
       </c>
       <c r="C44">
-        <v>3225.21</v>
+        <v>2097.9899999999998</v>
       </c>
       <c r="D44">
-        <v>8789.7000000000007</v>
+        <v>19221</v>
       </c>
       <c r="E44">
-        <v>34574.436379999999</v>
+        <v>68970.401014999996</v>
       </c>
       <c r="F44">
-        <v>9.3283082464524616E-2</v>
+        <v>3.0418700908288462E-2</v>
       </c>
       <c r="G44">
-        <v>1791.1166000000001</v>
+        <v>3149.8870999999999</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3396,19 +3035,19 @@
         <v>65</v>
       </c>
       <c r="C45">
-        <v>2917.86</v>
+        <v>1959.13</v>
       </c>
       <c r="D45">
-        <v>7476.5</v>
+        <v>18397.400000000001</v>
       </c>
       <c r="E45">
-        <v>24332.98</v>
+        <v>60332.212330000002</v>
       </c>
       <c r="F45">
-        <v>0.11991379600854481</v>
+        <v>3.247237129784198E-2</v>
       </c>
       <c r="G45">
-        <v>1496.4</v>
+        <v>2661.8912</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3419,19 +3058,19 @@
         <v>64</v>
       </c>
       <c r="C46">
-        <v>3537.15</v>
+        <v>1541.3</v>
       </c>
       <c r="D46">
-        <v>10089.1</v>
+        <v>14008</v>
       </c>
       <c r="E46">
-        <v>49470.3</v>
+        <v>30578.383760000001</v>
       </c>
       <c r="F46">
-        <v>7.1500476043201672E-2</v>
+        <v>5.0404887717322579E-2</v>
       </c>
       <c r="G46">
-        <v>2515.6</v>
+        <v>1591.3864000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3442,19 +3081,19 @@
         <v>65</v>
       </c>
       <c r="C47">
-        <v>3676.3200000000011</v>
+        <v>1845.01</v>
       </c>
       <c r="D47">
-        <v>9399.2000000000007</v>
+        <v>12324.1</v>
       </c>
       <c r="E47">
-        <v>72146.62</v>
+        <v>28972.17626</v>
       </c>
       <c r="F47">
-        <v>5.0956233292703122E-2</v>
+        <v>6.3682133625125203E-2</v>
       </c>
       <c r="G47">
-        <v>3403.4</v>
+        <v>1579.0164</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3465,19 +3104,19 @@
         <v>64</v>
       </c>
       <c r="C48">
-        <v>2511.64</v>
+        <v>1878.07</v>
       </c>
       <c r="D48">
-        <v>11717.3</v>
+        <v>10339.200000000001</v>
       </c>
       <c r="E48">
-        <v>62800.265520000001</v>
+        <v>77731.991270000013</v>
       </c>
       <c r="F48">
-        <v>3.9994098419856502E-2</v>
+        <v>2.4160837376165669E-2</v>
       </c>
       <c r="G48">
-        <v>2901.2664</v>
+        <v>3599.9164000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3488,19 +3127,19 @@
         <v>65</v>
       </c>
       <c r="C49">
-        <v>3013.06</v>
+        <v>1885.17</v>
       </c>
       <c r="D49">
-        <v>13367.2</v>
+        <v>8345.2000000000007</v>
       </c>
       <c r="E49">
-        <v>41293.012354999992</v>
+        <v>65302.776175000014</v>
       </c>
       <c r="F49">
-        <v>7.2967793536020911E-2</v>
+        <v>2.8868144823553508E-2</v>
       </c>
       <c r="G49">
-        <v>2236.7946999999999</v>
+        <v>3274.5495999999998</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3511,19 +3150,19 @@
         <v>64</v>
       </c>
       <c r="C50">
-        <v>3884.21</v>
+        <v>1895.73</v>
       </c>
       <c r="D50">
-        <v>12745</v>
+        <v>14384.1</v>
       </c>
       <c r="E50">
-        <v>73207.886205000003</v>
+        <v>31793.727500000001</v>
       </c>
       <c r="F50">
-        <v>5.3057262015778747E-2</v>
+        <v>5.9625912060798779E-2</v>
       </c>
       <c r="G50">
-        <v>3370.1338999999998</v>
+        <v>1666.925</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3534,19 +3173,19 @@
         <v>65</v>
       </c>
       <c r="C51">
-        <v>3053.87</v>
+        <v>1795.6</v>
       </c>
       <c r="D51">
-        <v>8540.5</v>
+        <v>14824.6</v>
       </c>
       <c r="E51">
-        <v>79590.437380000003</v>
+        <v>31722.03</v>
       </c>
       <c r="F51">
-        <v>3.8369810501473589E-2</v>
+        <v>5.6604195885320077E-2</v>
       </c>
       <c r="G51">
-        <v>4043.6578</v>
+        <v>1606.8050000000001</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3557,19 +3196,19 @@
         <v>64</v>
       </c>
       <c r="C52">
-        <v>2758.17</v>
+        <v>1451.53</v>
       </c>
       <c r="D52">
-        <v>5792.7</v>
+        <v>10263.700000000001</v>
       </c>
       <c r="E52">
-        <v>40921.86</v>
+        <v>34902.142500000002</v>
       </c>
       <c r="F52">
-        <v>6.7400895267223926E-2</v>
+        <v>4.1588564369651533E-2</v>
       </c>
       <c r="G52">
-        <v>2194.6</v>
+        <v>1916.5</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3580,19 +3219,19 @@
         <v>65</v>
       </c>
       <c r="C53">
-        <v>4889.34</v>
+        <v>1835.24</v>
       </c>
       <c r="D53">
-        <v>11660.5</v>
+        <v>11514.9</v>
       </c>
       <c r="E53">
-        <v>78465.759999999995</v>
+        <v>49389.237500000003</v>
       </c>
       <c r="F53">
-        <v>6.2311765029740368E-2</v>
+        <v>3.7158702844926478E-2</v>
       </c>
       <c r="G53">
-        <v>4226.3999999999996</v>
+        <v>2873.5749999999998</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3603,19 +3242,19 @@
         <v>64</v>
       </c>
       <c r="C54">
-        <v>2761.47</v>
+        <v>877.70000000000016</v>
       </c>
       <c r="D54">
-        <v>1510.4</v>
+        <v>5267.9</v>
       </c>
       <c r="E54">
-        <v>101270.88217500001</v>
+        <v>10586.1875</v>
       </c>
       <c r="F54">
-        <v>2.7268153892725779E-2</v>
+        <v>8.2909923898476207E-2</v>
       </c>
       <c r="G54">
-        <v>6936.6295</v>
+        <v>828.68500000000006</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3626,19 +3265,19 @@
         <v>65</v>
       </c>
       <c r="C55">
-        <v>3018.77</v>
+        <v>1792.24</v>
       </c>
       <c r="D55">
-        <v>1593.7</v>
+        <v>13850.1</v>
       </c>
       <c r="E55">
-        <v>132760.36825500001</v>
+        <v>28742.497500000001</v>
       </c>
       <c r="F55">
-        <v>2.273848769537673E-2</v>
+        <v>6.2355054566848263E-2</v>
       </c>
       <c r="G55">
-        <v>9092.3206999999984</v>
+        <v>1804.8050000000001</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3649,19 +3288,19 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>3433.26</v>
+        <v>1610.21</v>
       </c>
       <c r="D56">
-        <v>11612.8</v>
+        <v>8947.4000000000015</v>
       </c>
       <c r="E56">
-        <v>35745.1</v>
+        <v>28931.403040000001</v>
       </c>
       <c r="F56">
-        <v>9.6048409432341775E-2</v>
+        <v>5.5656132465257718E-2</v>
       </c>
       <c r="G56">
-        <v>2102.4</v>
+        <v>1423.5727999999999</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3672,19 +3311,19 @@
         <v>65</v>
       </c>
       <c r="C57">
-        <v>3635.58</v>
+        <v>1456.62</v>
       </c>
       <c r="D57">
-        <v>10878.5</v>
+        <v>7707.1</v>
       </c>
       <c r="E57">
-        <v>34115.1</v>
+        <v>17147.162499999999</v>
       </c>
       <c r="F57">
-        <v>0.1065680593051171</v>
+        <v>8.4948165622154667E-2</v>
       </c>
       <c r="G57">
-        <v>1842.6</v>
+        <v>1034.53</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3695,19 +3334,19 @@
         <v>64</v>
       </c>
       <c r="C58">
-        <v>3783.26</v>
+        <v>1632.64</v>
       </c>
       <c r="D58">
-        <v>16368.8</v>
+        <v>9252.1</v>
       </c>
       <c r="E58">
-        <v>75475.64</v>
+        <v>72459.730195000011</v>
       </c>
       <c r="F58">
-        <v>5.012557694111637E-2</v>
+        <v>2.2531687540187091E-2</v>
       </c>
       <c r="G58">
-        <v>3714.6</v>
+        <v>3471.6799000000001</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3718,19 +3357,19 @@
         <v>65</v>
       </c>
       <c r="C59">
-        <v>4232.47</v>
+        <v>1099.4100000000001</v>
       </c>
       <c r="D59">
-        <v>9563</v>
+        <v>6533.8</v>
       </c>
       <c r="E59">
-        <v>51125.42</v>
+        <v>27384.358564999999</v>
       </c>
       <c r="F59">
-        <v>8.2786019166199529E-2</v>
+        <v>4.0147370893878008E-2</v>
       </c>
       <c r="G59">
-        <v>2659.6</v>
+        <v>1489.6648</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3741,19 +3380,19 @@
         <v>64</v>
       </c>
       <c r="C60">
-        <v>3241.75</v>
+        <v>1296.8499999999999</v>
       </c>
       <c r="D60">
-        <v>10252.799999999999</v>
+        <v>7119.8</v>
       </c>
       <c r="E60">
-        <v>44148.969439999993</v>
+        <v>18164.005000000001</v>
       </c>
       <c r="F60">
-        <v>7.3427535027870874E-2</v>
+        <v>7.139669913105616E-2</v>
       </c>
       <c r="G60">
-        <v>2672.5255999999999</v>
+        <v>1150.875</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3764,19 +3403,19 @@
         <v>65</v>
       </c>
       <c r="C61">
-        <v>3724.59</v>
+        <v>1695.64</v>
       </c>
       <c r="D61">
-        <v>7943.4</v>
+        <v>8821.7999999999993</v>
       </c>
       <c r="E61">
-        <v>76528.307029999996</v>
+        <v>20551.764999999999</v>
       </c>
       <c r="F61">
-        <v>4.8669441995364111E-2</v>
+        <v>8.250580911177216E-2</v>
       </c>
       <c r="G61">
-        <v>4246.8986999999997</v>
+        <v>1484.2550000000001</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3787,19 +3426,19 @@
         <v>64</v>
       </c>
       <c r="C62">
-        <v>1466.65</v>
+        <v>1766.09</v>
       </c>
       <c r="D62">
-        <v>968</v>
+        <v>10372.6</v>
       </c>
       <c r="E62">
-        <v>47192.283454999997</v>
+        <v>48074.004999999997</v>
       </c>
       <c r="F62">
-        <v>3.1078174070524E-2</v>
+        <v>3.6736901782990612E-2</v>
       </c>
       <c r="G62">
-        <v>2599.3744999999999</v>
+        <v>2348.65</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3810,19 +3449,19 @@
         <v>65</v>
       </c>
       <c r="C63">
-        <v>4666.8600000000006</v>
+        <v>1835.99</v>
       </c>
       <c r="D63">
-        <v>1995.2</v>
+        <v>9847.2999999999993</v>
       </c>
       <c r="E63">
-        <v>182918.86882999999</v>
+        <v>78345.852500000008</v>
       </c>
       <c r="F63">
-        <v>2.5513278262929009E-2</v>
+        <v>2.3434424942915769E-2</v>
       </c>
       <c r="G63">
-        <v>8381.7383000000009</v>
+        <v>3443.8249999999998</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3833,19 +3472,19 @@
         <v>64</v>
       </c>
       <c r="C64">
-        <v>3987.5700000000011</v>
+        <v>1575.38</v>
       </c>
       <c r="D64">
-        <v>2709.6</v>
+        <v>11756.1</v>
       </c>
       <c r="E64">
-        <v>330332.09868499998</v>
+        <v>27163.102500000001</v>
       </c>
       <c r="F64">
-        <v>1.207139728737803E-2</v>
+        <v>5.7997056853133763E-2</v>
       </c>
       <c r="G64">
-        <v>13127.719499999999</v>
+        <v>1546.5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3856,19 +3495,19 @@
         <v>65</v>
       </c>
       <c r="C65">
-        <v>4716.25</v>
+        <v>1871.22</v>
       </c>
       <c r="D65">
-        <v>2082.1999999999998</v>
+        <v>13578.1</v>
       </c>
       <c r="E65">
-        <v>220651.29868000001</v>
+        <v>29311.342499999999</v>
       </c>
       <c r="F65">
-        <v>2.1374222713457729E-2</v>
+        <v>6.3839450547172993E-2</v>
       </c>
       <c r="G65">
-        <v>10743.317499999999</v>
+        <v>1555.57</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3879,19 +3518,19 @@
         <v>64</v>
       </c>
       <c r="C66">
-        <v>3980.64</v>
+        <v>1253.05</v>
       </c>
       <c r="D66">
-        <v>9104.4</v>
+        <v>8307.7999999999993</v>
       </c>
       <c r="E66">
-        <v>107590.088625</v>
+        <v>19801.654999999999</v>
       </c>
       <c r="F66">
-        <v>3.6998203560128347E-2</v>
+        <v>6.3280064216854601E-2</v>
       </c>
       <c r="G66">
-        <v>5503.6166999999996</v>
+        <v>1184.9000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3902,709 +3541,709 @@
         <v>65</v>
       </c>
       <c r="C67">
-        <v>3593.03</v>
+        <v>1542.85</v>
       </c>
       <c r="D67">
-        <v>5572.5</v>
+        <v>8399</v>
       </c>
       <c r="E67">
-        <v>86390.949785000004</v>
+        <v>17106.169999999998</v>
       </c>
       <c r="F67">
-        <v>4.1590351870675411E-2</v>
+        <v>9.0192603019846038E-2</v>
       </c>
       <c r="G67">
-        <v>4767.8874999999998</v>
+        <v>1104.4449999999999</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B68" t="s">
         <v>64</v>
       </c>
       <c r="C68">
-        <v>3417.93</v>
+        <v>1729.87</v>
       </c>
       <c r="D68">
-        <v>1285.2</v>
+        <v>9289.1</v>
       </c>
       <c r="E68">
-        <v>95092.408790000001</v>
+        <v>75820.736375000008</v>
       </c>
       <c r="F68">
-        <v>3.5943247662892662E-2</v>
+        <v>2.281526245596292E-2</v>
       </c>
       <c r="G68">
-        <v>6539.0006000000003</v>
+        <v>3444.9756000000002</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B69" t="s">
         <v>65</v>
       </c>
       <c r="C69">
-        <v>4909.91</v>
+        <v>1931.26</v>
       </c>
       <c r="D69">
-        <v>1938.5</v>
+        <v>5396.4</v>
       </c>
       <c r="E69">
-        <v>143231.18695</v>
+        <v>51365.120535000009</v>
       </c>
       <c r="F69">
-        <v>3.427961538651482E-2</v>
+        <v>3.7598665784966789E-2</v>
       </c>
       <c r="G69">
-        <v>7915.8431</v>
+        <v>2623.6187</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B70" t="s">
         <v>64</v>
       </c>
       <c r="C70">
-        <v>4337.2</v>
+        <v>1696.17</v>
       </c>
       <c r="D70">
-        <v>1507.7</v>
+        <v>12925.3</v>
       </c>
       <c r="E70">
-        <v>99141.559244999997</v>
+        <v>32473.115450000001</v>
       </c>
       <c r="F70">
-        <v>4.3747546770793178E-2</v>
+        <v>5.2233054220241132E-2</v>
       </c>
       <c r="G70">
-        <v>6775.5158000000001</v>
+        <v>1897.8675000000001</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
         <v>65</v>
       </c>
       <c r="C71">
-        <v>3558.42</v>
+        <v>1732.16</v>
       </c>
       <c r="D71">
-        <v>1732</v>
+        <v>11049.6</v>
       </c>
       <c r="E71">
-        <v>183172.32394</v>
+        <v>26116.541399999998</v>
       </c>
       <c r="F71">
-        <v>1.9426624740348859E-2</v>
+        <v>6.63242491978666E-2</v>
       </c>
       <c r="G71">
-        <v>9666.031500000001</v>
+        <v>1506.1859999999999</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
         <v>64</v>
       </c>
       <c r="C72">
-        <v>1876.1</v>
+        <v>1619.05</v>
       </c>
       <c r="D72">
-        <v>1212.4000000000001</v>
+        <v>10384.799999999999</v>
       </c>
       <c r="E72">
-        <v>98195.363774999991</v>
+        <v>34523.327550000002</v>
       </c>
       <c r="F72">
-        <v>1.910579000754865E-2</v>
+        <v>4.6897275404728482E-2</v>
       </c>
       <c r="G72">
-        <v>6627.4044999999996</v>
+        <v>2098.6869999999999</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
         <v>65</v>
       </c>
       <c r="C73">
-        <v>2413.77</v>
+        <v>1860.03</v>
       </c>
       <c r="D73">
-        <v>1731</v>
+        <v>8087.8</v>
       </c>
       <c r="E73">
-        <v>160337.62648499999</v>
+        <v>56809.242480000008</v>
       </c>
       <c r="F73">
-        <v>1.5054295444655429E-2</v>
+        <v>3.2741679325416689E-2</v>
       </c>
       <c r="G73">
-        <v>10948.7629</v>
+        <v>2923.1561999999999</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B74" t="s">
         <v>64</v>
       </c>
       <c r="C74">
-        <v>2881.26</v>
+        <v>1987.9</v>
       </c>
       <c r="D74">
-        <v>8999</v>
+        <v>9109.6</v>
       </c>
       <c r="E74">
-        <v>41384.68</v>
+        <v>99049.97000500001</v>
       </c>
       <c r="F74">
-        <v>6.9621415460987018E-2</v>
+        <v>2.0069667864610671E-2</v>
       </c>
       <c r="G74">
-        <v>2816.8</v>
+        <v>4519.8698000000004</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B75" t="s">
         <v>65</v>
       </c>
       <c r="C75">
-        <v>3664.05</v>
+        <v>1794.26</v>
       </c>
       <c r="D75">
-        <v>8569.2000000000007</v>
+        <v>5884.6</v>
       </c>
       <c r="E75">
-        <v>48032.34</v>
+        <v>70879.630680000002</v>
       </c>
       <c r="F75">
-        <v>7.6282979342667881E-2</v>
+        <v>2.5314183818204959E-2</v>
       </c>
       <c r="G75">
-        <v>2631.4</v>
+        <v>3308.4189999999999</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
         <v>64</v>
       </c>
       <c r="C76">
-        <v>3521.93</v>
+        <v>2072.87</v>
       </c>
       <c r="D76">
-        <v>1838.9</v>
+        <v>11912.1</v>
       </c>
       <c r="E76">
-        <v>251720.22570000001</v>
+        <v>114956.06628499999</v>
       </c>
       <c r="F76">
-        <v>1.399144621853881E-2</v>
+        <v>1.8031845269138942E-2</v>
       </c>
       <c r="G76">
-        <v>11970.881100000001</v>
+        <v>5280.6098999999986</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
         <v>65</v>
       </c>
       <c r="C77">
-        <v>4045.12</v>
+        <v>2203.87</v>
       </c>
       <c r="D77">
-        <v>1658.9</v>
+        <v>11281.7</v>
       </c>
       <c r="E77">
-        <v>129106.79841</v>
+        <v>116222.767185</v>
       </c>
       <c r="F77">
-        <v>3.1331580132241008E-2</v>
+        <v>1.8962463666795541E-2</v>
       </c>
       <c r="G77">
-        <v>6945.0796</v>
+        <v>5502.1479000000008</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s">
         <v>64</v>
       </c>
       <c r="C78">
-        <v>1312.92</v>
+        <v>1593.05</v>
       </c>
       <c r="D78">
-        <v>3160.3</v>
+        <v>8843.7999999999993</v>
       </c>
       <c r="E78">
-        <v>10187.200000000001</v>
+        <v>35285.05227</v>
       </c>
       <c r="F78">
-        <v>0.1288793780430344</v>
+        <v>4.5148013039913802E-2</v>
       </c>
       <c r="G78">
-        <v>642.6</v>
+        <v>1918.8527999999999</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B79" t="s">
         <v>65</v>
       </c>
       <c r="C79">
-        <v>3037.72</v>
+        <v>1457.04</v>
       </c>
       <c r="D79">
-        <v>7418.9</v>
+        <v>6901.1</v>
       </c>
       <c r="E79">
-        <v>35689.599999999999</v>
+        <v>22338.887500000001</v>
       </c>
       <c r="F79">
-        <v>8.5114991482112434E-2</v>
+        <v>6.5224376101988071E-2</v>
       </c>
       <c r="G79">
-        <v>1702.4</v>
+        <v>1219.92</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B80" t="s">
         <v>64</v>
       </c>
       <c r="C80">
-        <v>3279.71</v>
+        <v>1825.47</v>
       </c>
       <c r="D80">
-        <v>11375</v>
+        <v>12481.7</v>
       </c>
       <c r="E80">
-        <v>35521.365129999998</v>
+        <v>50943.82</v>
       </c>
       <c r="F80">
-        <v>9.2330629411257664E-2</v>
+        <v>3.5833001922509933E-2</v>
       </c>
       <c r="G80">
-        <v>1856.3947000000001</v>
+        <v>2548.9349999999999</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B81" t="s">
         <v>65</v>
       </c>
       <c r="C81">
-        <v>3066.48</v>
+        <v>1993.11</v>
       </c>
       <c r="D81">
-        <v>10222.4</v>
+        <v>9876.1</v>
       </c>
       <c r="E81">
-        <v>34387.759999999987</v>
+        <v>60078.080000000002</v>
       </c>
       <c r="F81">
-        <v>8.9173589672604456E-2</v>
+        <v>3.3175327840037502E-2</v>
       </c>
       <c r="G81">
-        <v>1761.4</v>
+        <v>2845.7249999999999</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B82" t="s">
         <v>64</v>
       </c>
       <c r="C82">
-        <v>3772.2999999999988</v>
+        <v>1830.05</v>
       </c>
       <c r="D82">
-        <v>16178</v>
+        <v>13673.3</v>
       </c>
       <c r="E82">
-        <v>72544.98</v>
+        <v>78236.819940000016</v>
       </c>
       <c r="F82">
-        <v>5.1999462953880471E-2</v>
+        <v>2.3391160343729071E-2</v>
       </c>
       <c r="G82">
-        <v>3428.4</v>
+        <v>3113.884</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
         <v>65</v>
       </c>
       <c r="C83">
-        <v>3826.96</v>
+        <v>1550.68</v>
       </c>
       <c r="D83">
-        <v>12518.6</v>
+        <v>10052</v>
       </c>
       <c r="E83">
-        <v>69154.5</v>
+        <v>51687.796950000004</v>
       </c>
       <c r="F83">
-        <v>5.5339276547440877E-2</v>
+        <v>3.0000891728855169E-2</v>
       </c>
       <c r="G83">
-        <v>3513.6</v>
+        <v>2071.0207</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
         <v>64</v>
       </c>
       <c r="C84">
-        <v>4199.84</v>
+        <v>1716.05</v>
       </c>
       <c r="D84">
-        <v>18629.3</v>
+        <v>7656</v>
       </c>
       <c r="E84">
-        <v>86202.434325000009</v>
+        <v>79480.771530000027</v>
       </c>
       <c r="F84">
-        <v>4.8720665870824291E-2</v>
+        <v>2.1590756694558219E-2</v>
       </c>
       <c r="G84">
-        <v>4029.1804999999999</v>
+        <v>3215.8816000000002</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B85" t="s">
         <v>65</v>
       </c>
       <c r="C85">
-        <v>3921.9800000000009</v>
+        <v>1480.05</v>
       </c>
       <c r="D85">
-        <v>17752.599999999999</v>
+        <v>3081.2</v>
       </c>
       <c r="E85">
-        <v>75593.683139999994</v>
+        <v>31238.675050000009</v>
       </c>
       <c r="F85">
-        <v>5.1882377430088548E-2</v>
+        <v>4.7378769990438503E-2</v>
       </c>
       <c r="G85">
-        <v>3586.2595999999999</v>
+        <v>1458.3314</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
         <v>64</v>
       </c>
       <c r="C86">
-        <v>3086.98</v>
+        <v>1629.1</v>
       </c>
       <c r="D86">
-        <v>13736.5</v>
+        <v>11593.5</v>
       </c>
       <c r="E86">
-        <v>42749.232354999993</v>
+        <v>28029.123759999999</v>
       </c>
       <c r="F86">
-        <v>7.2211355150543277E-2</v>
+        <v>5.8121688496194347E-2</v>
       </c>
       <c r="G86">
-        <v>2216.9947000000002</v>
+        <v>1792.9313999999999</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
         <v>65</v>
       </c>
       <c r="C87">
-        <v>3694.93</v>
+        <v>1941.74</v>
       </c>
       <c r="D87">
-        <v>11978.7</v>
+        <v>10028</v>
       </c>
       <c r="E87">
-        <v>39489.332354999999</v>
+        <v>44008.276220000007</v>
       </c>
       <c r="F87">
-        <v>9.3567801217387794E-2</v>
+        <v>4.4122155348533212E-2</v>
       </c>
       <c r="G87">
-        <v>2184.9947000000002</v>
+        <v>2004.5111999999999</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
         <v>64</v>
       </c>
       <c r="C88">
-        <v>3760.53</v>
+        <v>1714.83</v>
       </c>
       <c r="D88">
-        <v>10690.1</v>
+        <v>11915.9</v>
       </c>
       <c r="E88">
-        <v>93486.512524999998</v>
+        <v>27851.365000000002</v>
       </c>
       <c r="F88">
-        <v>4.0225374745842243E-2</v>
+        <v>6.1570770409277963E-2</v>
       </c>
       <c r="G88">
-        <v>4632.4377000000004</v>
+        <v>1650.95</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
         <v>65</v>
       </c>
       <c r="C89">
-        <v>3776.09</v>
+        <v>1815.46</v>
       </c>
       <c r="D89">
-        <v>7784.4000000000005</v>
+        <v>11190.5</v>
       </c>
       <c r="E89">
-        <v>75955.048855000001</v>
+        <v>24440.342499999999</v>
       </c>
       <c r="F89">
-        <v>4.9714799172977241E-2</v>
+        <v>7.4281283087583569E-2</v>
       </c>
       <c r="G89">
-        <v>4216.3634000000002</v>
+        <v>1293.9100000000001</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B90" t="s">
         <v>64</v>
       </c>
       <c r="C90">
-        <v>3795</v>
+        <v>2001.56</v>
       </c>
       <c r="D90">
-        <v>14046.2</v>
+        <v>12949.7</v>
       </c>
       <c r="E90">
-        <v>45375.839999999997</v>
+        <v>78926.658580000003</v>
       </c>
       <c r="F90">
-        <v>8.3634815355484338E-2</v>
+        <v>2.5359745819864148E-2</v>
       </c>
       <c r="G90">
-        <v>2365.6</v>
+        <v>3553.0455999999999</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B91" t="s">
         <v>65</v>
       </c>
       <c r="C91">
-        <v>3594.81</v>
+        <v>1895.79</v>
       </c>
       <c r="D91">
-        <v>14407.5</v>
+        <v>10748.8</v>
       </c>
       <c r="E91">
-        <v>45888.3</v>
+        <v>47159.96</v>
       </c>
       <c r="F91">
-        <v>7.833826923202647E-2</v>
+        <v>4.0199143510723928E-2</v>
       </c>
       <c r="G91">
-        <v>2350</v>
+        <v>2572.0250000000001</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B92" t="s">
         <v>64</v>
       </c>
       <c r="C92">
-        <v>2906.91</v>
+        <v>1889.7</v>
       </c>
       <c r="D92">
-        <v>10025.5</v>
+        <v>16114.5</v>
       </c>
       <c r="E92">
-        <v>41520.1</v>
+        <v>65389.137499999997</v>
       </c>
       <c r="F92">
-        <v>7.0012114614367502E-2</v>
+        <v>2.8899295391379039E-2</v>
       </c>
       <c r="G92">
-        <v>2310.8000000000002</v>
+        <v>3136.0749999999998</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
         <v>65</v>
       </c>
       <c r="C93">
-        <v>3674.68</v>
+        <v>2113.88</v>
       </c>
       <c r="D93">
-        <v>11183.2</v>
+        <v>9866.9</v>
       </c>
       <c r="E93">
-        <v>52831.38</v>
+        <v>49908.567499999997</v>
       </c>
       <c r="F93">
-        <v>6.9554874394725255E-2</v>
+        <v>4.2355052566876418E-2</v>
       </c>
       <c r="G93">
-        <v>3027.6</v>
+        <v>2360.7750000000001</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B94" t="s">
         <v>64</v>
       </c>
       <c r="C94">
-        <v>1760.92</v>
+        <v>1377.62</v>
       </c>
       <c r="D94">
-        <v>5140.1000000000004</v>
+        <v>1510.4</v>
       </c>
       <c r="E94">
-        <v>15696.88</v>
+        <v>41732.358419999997</v>
       </c>
       <c r="F94">
-        <v>0.1121828032067519</v>
+        <v>3.3010835048799543E-2</v>
       </c>
       <c r="G94">
-        <v>1124.4000000000001</v>
+        <v>2873.7887999999998</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B95" t="s">
         <v>65</v>
       </c>
       <c r="C95">
-        <v>3588.07</v>
+        <v>1506.42</v>
       </c>
       <c r="D95">
-        <v>13473.1</v>
+        <v>1593.7</v>
       </c>
       <c r="E95">
-        <v>41857.82</v>
+        <v>36258.469835000004</v>
       </c>
       <c r="F95">
-        <v>8.5720422133785265E-2</v>
+        <v>4.1546706379370288E-2</v>
       </c>
       <c r="G95">
-        <v>2541.4</v>
+        <v>2505.5819000000001</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B96" t="s">
         <v>64</v>
       </c>
       <c r="C96">
-        <v>2510.16</v>
+        <v>1252.56</v>
       </c>
       <c r="D96">
-        <v>8111.9</v>
+        <v>11946.4</v>
       </c>
       <c r="E96">
-        <v>26261.26</v>
+        <v>59203.297160000016</v>
       </c>
       <c r="F96">
-        <v>9.5584141811931339E-2</v>
+        <v>2.1156929767186632E-2</v>
       </c>
       <c r="G96">
-        <v>1626</v>
+        <v>2569.2161999999998</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
         <v>65</v>
       </c>
       <c r="C97">
-        <v>3089.33</v>
+        <v>1502.95</v>
       </c>
       <c r="D97">
-        <v>8166.5</v>
+        <v>13704</v>
       </c>
       <c r="E97">
-        <v>25670.98</v>
+        <v>30534.396260000001</v>
       </c>
       <c r="F97">
-        <v>0.1203432825704356</v>
+        <v>4.9221539774436662E-2</v>
       </c>
       <c r="G97">
-        <v>1622.8</v>
+        <v>1650.4764</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4615,19 +4254,19 @@
         <v>64</v>
       </c>
       <c r="C98">
-        <v>4150</v>
+        <v>1939.92</v>
       </c>
       <c r="D98">
-        <v>11390.9</v>
+        <v>13153.5</v>
       </c>
       <c r="E98">
-        <v>125628.44931500001</v>
+        <v>73733.344920000003</v>
       </c>
       <c r="F98">
-        <v>3.3033918850612541E-2</v>
+        <v>2.630994161603268E-2</v>
       </c>
       <c r="G98">
-        <v>6334.4490999999998</v>
+        <v>3273.0054</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4638,19 +4277,19 @@
         <v>65</v>
       </c>
       <c r="C99">
-        <v>4412.13</v>
+        <v>1525.16</v>
       </c>
       <c r="D99">
-        <v>10554.2</v>
+        <v>8548.1</v>
       </c>
       <c r="E99">
-        <v>113208.150455</v>
+        <v>57486.83430000001</v>
       </c>
       <c r="F99">
-        <v>3.8973607308899663E-2</v>
+        <v>2.6530596415186489E-2</v>
       </c>
       <c r="G99">
-        <v>5874.7797</v>
+        <v>2496.3703</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4661,19 +4300,19 @@
         <v>64</v>
       </c>
       <c r="C100">
-        <v>3009.07</v>
+        <v>1375.93</v>
       </c>
       <c r="D100">
-        <v>1515.5</v>
+        <v>5919.7</v>
       </c>
       <c r="E100">
-        <v>119176.45017500001</v>
+        <v>44657.377500000002</v>
       </c>
       <c r="F100">
-        <v>2.5248864147081478E-2</v>
+        <v>3.0810810598987812E-2</v>
       </c>
       <c r="G100">
-        <v>6872.7923999999994</v>
+        <v>2547.5</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4684,19 +4323,19 @@
         <v>65</v>
       </c>
       <c r="C101">
-        <v>3934.64</v>
+        <v>2441.0700000000002</v>
       </c>
       <c r="D101">
-        <v>1726.1</v>
+        <v>11938.5</v>
       </c>
       <c r="E101">
-        <v>148265.96614999999</v>
+        <v>91163.755000000005</v>
       </c>
       <c r="F101">
-        <v>2.6537715311006321E-2</v>
+        <v>2.6776760127969718E-2</v>
       </c>
       <c r="G101">
-        <v>7791.5955999999996</v>
+        <v>4955.9650000000001</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4707,19 +4346,19 @@
         <v>64</v>
       </c>
       <c r="C102">
-        <v>3395.81</v>
+        <v>1133.0899999999999</v>
       </c>
       <c r="D102">
-        <v>12695.7</v>
+        <v>8670.2999999999993</v>
       </c>
       <c r="E102">
-        <v>56728.410174999997</v>
+        <v>30808.247500000001</v>
       </c>
       <c r="F102">
-        <v>5.9860834977119123E-2</v>
+        <v>3.6778787887886202E-2</v>
       </c>
       <c r="G102">
-        <v>3330.2604999999999</v>
+        <v>1467.65</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4730,19 +4369,19 @@
         <v>65</v>
       </c>
       <c r="C103">
-        <v>3468.64</v>
+        <v>2216.98</v>
       </c>
       <c r="D103">
-        <v>10765.8</v>
+        <v>15548.3</v>
       </c>
       <c r="E103">
-        <v>45053.455750000001</v>
+        <v>58490.749609999999</v>
       </c>
       <c r="F103">
-        <v>7.6989432714048789E-2</v>
+        <v>3.7903087493017351E-2</v>
       </c>
       <c r="G103">
-        <v>2544.4924999999998</v>
+        <v>2884.4675999999999</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4753,19 +4392,19 @@
         <v>64</v>
       </c>
       <c r="C104">
-        <v>4007.73</v>
+        <v>1501.58</v>
       </c>
       <c r="D104">
-        <v>12815.7</v>
+        <v>1524.5</v>
       </c>
       <c r="E104">
-        <v>84425.412759999992</v>
+        <v>47789.434735000003</v>
       </c>
       <c r="F104">
-        <v>4.7470659236134957E-2</v>
+        <v>3.1420752480679028E-2</v>
       </c>
       <c r="G104">
-        <v>3974.0331999999999</v>
+        <v>2586.1275999999998</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4776,19 +4415,19 @@
         <v>65</v>
       </c>
       <c r="C105">
-        <v>3796.39</v>
+        <v>1964.09</v>
       </c>
       <c r="D105">
-        <v>10460.9</v>
+        <v>1729.1</v>
       </c>
       <c r="E105">
-        <v>52700.46</v>
+        <v>60906.200789999988</v>
       </c>
       <c r="F105">
-        <v>7.2037132123704425E-2</v>
+        <v>3.2247783879543468E-2</v>
       </c>
       <c r="G105">
-        <v>2751.6</v>
+        <v>3563.9938999999999</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4799,19 +4438,19 @@
         <v>64</v>
       </c>
       <c r="C106">
-        <v>3436.29</v>
+        <v>1757.61</v>
       </c>
       <c r="D106">
-        <v>7537.9</v>
+        <v>1841.9</v>
       </c>
       <c r="E106">
-        <v>94338.835135000001</v>
+        <v>65107.047120000003</v>
       </c>
       <c r="F106">
-        <v>3.6424978060017682E-2</v>
+        <v>2.6995695208853761E-2</v>
       </c>
       <c r="G106">
-        <v>4367.9426999999996</v>
+        <v>3539.1318000000001</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4822,65 +4461,65 @@
         <v>65</v>
       </c>
       <c r="C107">
-        <v>2964.01</v>
+        <v>2018.86</v>
       </c>
       <c r="D107">
-        <v>3053.2</v>
+        <v>1666.4</v>
       </c>
       <c r="E107">
-        <v>49389.385674999998</v>
+        <v>47769.764560000003</v>
       </c>
       <c r="F107">
-        <v>6.0013097135976877E-2</v>
+        <v>4.2262297471955562E-2</v>
       </c>
       <c r="G107">
-        <v>2580.6703000000002</v>
+        <v>2883.7310000000002</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B108" t="s">
         <v>64</v>
       </c>
       <c r="C108">
-        <v>3228.25</v>
+        <v>1612.06</v>
       </c>
       <c r="D108">
-        <v>10377.700000000001</v>
+        <v>10638.4</v>
       </c>
       <c r="E108">
-        <v>38401.428734999987</v>
+        <v>31942.435310000001</v>
       </c>
       <c r="F108">
-        <v>8.4065882607583672E-2</v>
+        <v>5.046766110207393E-2</v>
       </c>
       <c r="G108">
-        <v>2188.9113000000002</v>
+        <v>1718.2506000000001</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B109" t="s">
         <v>65</v>
       </c>
       <c r="C109">
-        <v>2955.41</v>
+        <v>1475.96</v>
       </c>
       <c r="D109">
-        <v>7923.5</v>
+        <v>8150.7</v>
       </c>
       <c r="E109">
-        <v>27266.36</v>
+        <v>21516.7075</v>
       </c>
       <c r="F109">
-        <v>0.10839033886444691</v>
+        <v>6.8595996855002089E-2</v>
       </c>
       <c r="G109">
-        <v>1667.8</v>
+        <v>1273.345</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4891,19 +4530,19 @@
         <v>64</v>
       </c>
       <c r="C110">
-        <v>2639.33</v>
+        <v>1317.32</v>
       </c>
       <c r="D110">
         <v>1424.8</v>
       </c>
       <c r="E110">
-        <v>122182.84032</v>
+        <v>42151.288235</v>
       </c>
       <c r="F110">
-        <v>2.1601478514393081E-2</v>
+        <v>3.1252188370987283E-2</v>
       </c>
       <c r="G110">
-        <v>8384.8047999999999</v>
+        <v>2916.7579000000001</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4914,19 +4553,19 @@
         <v>65</v>
       </c>
       <c r="C111">
-        <v>3206.71</v>
+        <v>1600.9</v>
       </c>
       <c r="D111">
         <v>1652.3</v>
       </c>
       <c r="E111">
-        <v>91124.178074999989</v>
+        <v>34827.209244999998</v>
       </c>
       <c r="F111">
-        <v>3.5190550606236569E-2</v>
+        <v>4.5966933173947448E-2</v>
       </c>
       <c r="G111">
-        <v>6241.1554999999998</v>
+        <v>2393.9542999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4940,10 +4579,10 @@
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4965,10 +4604,10 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>1.264468119049209E-2</v>
+        <v>2.189274255938432E-2</v>
       </c>
       <c r="C2">
-        <v>2.141966230342535E-2</v>
+        <v>3.2400437988086173E-2</v>
       </c>
       <c r="D2" t="s">
         <v>67</v>
@@ -4979,10 +4618,10 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>4.2813216149093003E-2</v>
+        <v>2.827658591258984E-2</v>
       </c>
       <c r="C3">
-        <v>6.1502038941400369E-2</v>
+        <v>4.2892121171974509E-2</v>
       </c>
       <c r="D3" t="s">
         <v>67</v>
@@ -4993,10 +4632,10 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.0884827110391077E-2</v>
+        <v>2.3402627071723522E-2</v>
       </c>
       <c r="C4">
-        <v>4.6222026603408989E-2</v>
+        <v>3.3951880882296608E-2</v>
       </c>
       <c r="D4" t="s">
         <v>67</v>
@@ -5007,10 +4646,10 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>1.4096167600742039E-2</v>
+        <v>2.180008079979362E-2</v>
       </c>
       <c r="C5">
-        <v>1.5401205321059911E-2</v>
+        <v>2.9938384625488149E-2</v>
       </c>
       <c r="D5" t="s">
         <v>67</v>
@@ -5021,13 +4660,13 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>6.5928162917207669E-2</v>
+        <v>2.8725493115484269E-2</v>
       </c>
       <c r="C6">
-        <v>6.8164737969039713E-2</v>
+        <v>2.704243139186352E-2</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5035,10 +4674,10 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>3.1814663873935563E-2</v>
+        <v>2.4198529113788739E-2</v>
       </c>
       <c r="C7">
-        <v>5.350164853668915E-2</v>
+        <v>3.4475102078342548E-2</v>
       </c>
       <c r="D7" t="s">
         <v>67</v>
@@ -5049,10 +4688,10 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>2.09412974103605E-2</v>
+        <v>2.6067447147161821E-2</v>
       </c>
       <c r="C8">
-        <v>2.7637051584490389E-2</v>
+        <v>3.7155792023522378E-2</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
@@ -5063,10 +4702,10 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>2.795172534764527E-2</v>
+        <v>2.8031433290968799E-2</v>
       </c>
       <c r="C9">
-        <v>3.8453797971824889E-2</v>
+        <v>5.1753453547221051E-2</v>
       </c>
       <c r="D9" t="s">
         <v>67</v>
@@ -5077,10 +4716,10 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.1056945509361229</v>
+        <v>2.8301746996093009E-2</v>
       </c>
       <c r="C10">
-        <v>0.11315327840553881</v>
+        <v>3.373134684977331E-2</v>
       </c>
       <c r="D10" t="s">
         <v>67</v>
@@ -5091,10 +4730,10 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>1.3978062494172E-2</v>
+        <v>2.3383865458063601E-2</v>
       </c>
       <c r="C11">
-        <v>1.6118707926384611E-2</v>
+        <v>3.2850542338489268E-2</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
@@ -5105,13 +4744,13 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>1.792873801950582E-2</v>
+        <v>3.6398995066968427E-2</v>
       </c>
       <c r="C12">
-        <v>2.1220237048942402E-2</v>
+        <v>3.595221583584416E-2</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5119,13 +4758,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>8.8574991259867508E-2</v>
+        <v>4.1165318053383228E-2</v>
       </c>
       <c r="C13">
-        <v>7.9581412495201981E-2</v>
+        <v>4.2306178003717818E-2</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5133,10 +4772,10 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>8.5356049757003241E-2</v>
+        <v>2.7818450889857509E-2</v>
       </c>
       <c r="C14">
-        <v>0.11321834353867111</v>
+        <v>3.5425803344756653E-2</v>
       </c>
       <c r="D14" t="s">
         <v>67</v>
@@ -5147,10 +4786,10 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>1.639489095810371E-2</v>
+        <v>2.3006193006997841E-2</v>
       </c>
       <c r="C15">
-        <v>2.3972170819988731E-2</v>
+        <v>3.3697059492407852E-2</v>
       </c>
       <c r="D15" t="s">
         <v>67</v>
@@ -5161,13 +4800,13 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>3.7561337735716682E-2</v>
+        <v>2.9232853072247631E-2</v>
       </c>
       <c r="C16">
-        <v>3.583598628899725E-2</v>
+        <v>4.0360339449610642E-2</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5175,10 +4814,10 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>1.5862692142661769E-2</v>
+        <v>2.7660827082417482E-2</v>
       </c>
       <c r="C17">
-        <v>2.5418946700488689E-2</v>
+        <v>3.1491502832890199E-2</v>
       </c>
       <c r="D17" t="s">
         <v>67</v>
@@ -5189,13 +4828,13 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>8.8549052656857946E-2</v>
+        <v>3.1853309583802163E-2</v>
       </c>
       <c r="C18">
-        <v>8.4826078416532433E-2</v>
+        <v>3.4131655383014978E-2</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5203,10 +4842,10 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>3.7673283501729903E-2</v>
+        <v>4.0613690073374883E-2</v>
       </c>
       <c r="C19">
-        <v>3.6210999592999782E-2</v>
+        <v>3.8873613964113228E-2</v>
       </c>
       <c r="D19" t="s">
         <v>68</v>
@@ -5217,13 +4856,13 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>2.531656423823455E-2</v>
+        <v>8.4297812415850992E-2</v>
       </c>
       <c r="C20">
-        <v>3.1052487271466089E-2</v>
+        <v>5.8594353978791661E-2</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5231,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>4.547969877422952E-2</v>
+        <v>6.3450654170347356E-2</v>
       </c>
       <c r="C21">
-        <v>5.6443544909543203E-2</v>
+        <v>6.0577788150934973E-2</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5245,10 +4884,10 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>6.0999662501316672E-2</v>
+        <v>3.3313253145171799E-2</v>
       </c>
       <c r="C22">
-        <v>5.7757649878251882E-2</v>
+        <v>2.8617095514515429E-2</v>
       </c>
       <c r="D22" t="s">
         <v>68</v>
@@ -5259,10 +4898,10 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>9.3283082464524616E-2</v>
+        <v>3.0418700908288462E-2</v>
       </c>
       <c r="C23">
-        <v>0.11991379600854481</v>
+        <v>3.247237129784198E-2</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -5273,13 +4912,13 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>7.1500476043201672E-2</v>
+        <v>5.0404887717322579E-2</v>
       </c>
       <c r="C24">
-        <v>5.0956233292703122E-2</v>
+        <v>6.3682133625125203E-2</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5287,10 +4926,10 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>3.9994098419856502E-2</v>
+        <v>2.4160837376165669E-2</v>
       </c>
       <c r="C25">
-        <v>7.2967793536020911E-2</v>
+        <v>2.8868144823553508E-2</v>
       </c>
       <c r="D25" t="s">
         <v>67</v>
@@ -5301,10 +4940,10 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>5.3057262015778747E-2</v>
+        <v>5.9625912060798779E-2</v>
       </c>
       <c r="C26">
-        <v>3.8369810501473589E-2</v>
+        <v>5.6604195885320077E-2</v>
       </c>
       <c r="D26" t="s">
         <v>68</v>
@@ -5315,10 +4954,10 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>6.7400895267223926E-2</v>
+        <v>4.1588564369651533E-2</v>
       </c>
       <c r="C27">
-        <v>6.2311765029740368E-2</v>
+        <v>3.7158702844926478E-2</v>
       </c>
       <c r="D27" t="s">
         <v>68</v>
@@ -5329,10 +4968,10 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>2.7268153892725779E-2</v>
+        <v>8.2909923898476207E-2</v>
       </c>
       <c r="C28">
-        <v>2.273848769537673E-2</v>
+        <v>6.2355054566848263E-2</v>
       </c>
       <c r="D28" t="s">
         <v>68</v>
@@ -5343,10 +4982,10 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>9.6048409432341775E-2</v>
+        <v>5.5656132465257718E-2</v>
       </c>
       <c r="C29">
-        <v>0.1065680593051171</v>
+        <v>8.4948165622154667E-2</v>
       </c>
       <c r="D29" t="s">
         <v>67</v>
@@ -5357,10 +4996,10 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>5.012557694111637E-2</v>
+        <v>2.2531687540187091E-2</v>
       </c>
       <c r="C30">
-        <v>8.2786019166199529E-2</v>
+        <v>4.0147370893878008E-2</v>
       </c>
       <c r="D30" t="s">
         <v>67</v>
@@ -5371,13 +5010,13 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>7.3427535027870874E-2</v>
+        <v>7.139669913105616E-2</v>
       </c>
       <c r="C31">
-        <v>4.8669441995364111E-2</v>
+        <v>8.250580911177216E-2</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5385,10 +5024,10 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>3.1078174070524E-2</v>
+        <v>3.6736901782990612E-2</v>
       </c>
       <c r="C32">
-        <v>2.5513278262929009E-2</v>
+        <v>2.3434424942915769E-2</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
@@ -5399,10 +5038,10 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>1.207139728737803E-2</v>
+        <v>5.7997056853133763E-2</v>
       </c>
       <c r="C33">
-        <v>2.1374222713457729E-2</v>
+        <v>6.3839450547172993E-2</v>
       </c>
       <c r="D33" t="s">
         <v>67</v>
@@ -5413,10 +5052,10 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>3.6998203560128347E-2</v>
+        <v>6.3280064216854601E-2</v>
       </c>
       <c r="C34">
-        <v>4.1590351870675411E-2</v>
+        <v>9.0192603019846038E-2</v>
       </c>
       <c r="D34" t="s">
         <v>67</v>
@@ -5424,41 +5063,41 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>3.5943247662892662E-2</v>
+        <v>2.281526245596292E-2</v>
       </c>
       <c r="C35">
-        <v>3.427961538651482E-2</v>
+        <v>3.7598665784966789E-2</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>4.3747546770793178E-2</v>
+        <v>5.2233054220241132E-2</v>
       </c>
       <c r="C36">
-        <v>1.9426624740348859E-2</v>
+        <v>6.63242491978666E-2</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37">
-        <v>1.910579000754865E-2</v>
+        <v>4.6897275404728482E-2</v>
       </c>
       <c r="C37">
-        <v>1.5054295444655429E-2</v>
+        <v>3.2741679325416689E-2</v>
       </c>
       <c r="D37" t="s">
         <v>68</v>
@@ -5466,13 +5105,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38">
-        <v>6.9621415460987018E-2</v>
+        <v>2.0069667864610671E-2</v>
       </c>
       <c r="C38">
-        <v>7.6282979342667881E-2</v>
+        <v>2.5314183818204959E-2</v>
       </c>
       <c r="D38" t="s">
         <v>67</v>
@@ -5480,13 +5119,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39">
-        <v>1.399144621853881E-2</v>
+        <v>1.8031845269138942E-2</v>
       </c>
       <c r="C39">
-        <v>3.1331580132241008E-2</v>
+        <v>1.8962463666795541E-2</v>
       </c>
       <c r="D39" t="s">
         <v>67</v>
@@ -5494,27 +5133,27 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40">
-        <v>0.1288793780430344</v>
+        <v>4.5148013039913802E-2</v>
       </c>
       <c r="C40">
-        <v>8.5114991482112434E-2</v>
+        <v>6.5224376101988071E-2</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>9.2330629411257664E-2</v>
+        <v>3.5833001922509933E-2</v>
       </c>
       <c r="C41">
-        <v>8.9173589672604456E-2</v>
+        <v>3.3175327840037502E-2</v>
       </c>
       <c r="D41" t="s">
         <v>68</v>
@@ -5522,13 +5161,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>5.1999462953880471E-2</v>
+        <v>2.3391160343729071E-2</v>
       </c>
       <c r="C42">
-        <v>5.5339276547440877E-2</v>
+        <v>3.0000891728855169E-2</v>
       </c>
       <c r="D42" t="s">
         <v>67</v>
@@ -5536,13 +5175,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
-        <v>4.8720665870824291E-2</v>
+        <v>2.1590756694558219E-2</v>
       </c>
       <c r="C43">
-        <v>5.1882377430088548E-2</v>
+        <v>4.7378769990438503E-2</v>
       </c>
       <c r="D43" t="s">
         <v>67</v>
@@ -5550,27 +5189,27 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44">
-        <v>7.2211355150543277E-2</v>
+        <v>5.8121688496194347E-2</v>
       </c>
       <c r="C44">
-        <v>9.3567801217387794E-2</v>
+        <v>4.4122155348533212E-2</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
-        <v>4.0225374745842243E-2</v>
+        <v>6.1570770409277963E-2</v>
       </c>
       <c r="C45">
-        <v>4.9714799172977241E-2</v>
+        <v>7.4281283087583569E-2</v>
       </c>
       <c r="D45" t="s">
         <v>67</v>
@@ -5578,55 +5217,55 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>8.3634815355484338E-2</v>
+        <v>2.5359745819864148E-2</v>
       </c>
       <c r="C46">
-        <v>7.833826923202647E-2</v>
+        <v>4.0199143510723928E-2</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47">
-        <v>7.0012114614367502E-2</v>
+        <v>2.8899295391379039E-2</v>
       </c>
       <c r="C47">
-        <v>6.9554874394725255E-2</v>
+        <v>4.2355052566876418E-2</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48">
-        <v>0.1121828032067519</v>
+        <v>3.3010835048799543E-2</v>
       </c>
       <c r="C48">
-        <v>8.5720422133785265E-2</v>
+        <v>4.1546706379370288E-2</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49">
-        <v>9.5584141811931339E-2</v>
+        <v>2.1156929767186632E-2</v>
       </c>
       <c r="C49">
-        <v>0.1203432825704356</v>
+        <v>4.9221539774436662E-2</v>
       </c>
       <c r="D49" t="s">
         <v>67</v>
@@ -5637,10 +5276,10 @@
         <v>56</v>
       </c>
       <c r="B50">
-        <v>3.3033918850612541E-2</v>
+        <v>2.630994161603268E-2</v>
       </c>
       <c r="C50">
-        <v>3.8973607308899663E-2</v>
+        <v>2.6530596415186489E-2</v>
       </c>
       <c r="D50" t="s">
         <v>67</v>
@@ -5651,13 +5290,13 @@
         <v>57</v>
       </c>
       <c r="B51">
-        <v>2.5248864147081478E-2</v>
+        <v>3.0810810598987812E-2</v>
       </c>
       <c r="C51">
-        <v>2.6537715311006321E-2</v>
+        <v>2.6776760127969718E-2</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -5665,10 +5304,10 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>5.9860834977119123E-2</v>
+        <v>3.6778787887886202E-2</v>
       </c>
       <c r="C52">
-        <v>7.6989432714048789E-2</v>
+        <v>3.7903087493017351E-2</v>
       </c>
       <c r="D52" t="s">
         <v>67</v>
@@ -5679,10 +5318,10 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>4.7470659236134957E-2</v>
+        <v>3.1420752480679028E-2</v>
       </c>
       <c r="C53">
-        <v>7.2037132123704425E-2</v>
+        <v>3.2247783879543468E-2</v>
       </c>
       <c r="D53" t="s">
         <v>67</v>
@@ -5693,10 +5332,10 @@
         <v>60</v>
       </c>
       <c r="B54">
-        <v>3.6424978060017682E-2</v>
+        <v>2.6995695208853761E-2</v>
       </c>
       <c r="C54">
-        <v>6.0013097135976877E-2</v>
+        <v>4.2262297471955562E-2</v>
       </c>
       <c r="D54" t="s">
         <v>67</v>
@@ -5704,13 +5343,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B55">
-        <v>8.4065882607583672E-2</v>
+        <v>5.046766110207393E-2</v>
       </c>
       <c r="C55">
-        <v>0.10839033886444691</v>
+        <v>6.8595996855002089E-2</v>
       </c>
       <c r="D55" t="s">
         <v>67</v>
@@ -5721,10 +5360,10 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>2.1601478514393081E-2</v>
+        <v>3.1252188370987283E-2</v>
       </c>
       <c r="C56">
-        <v>3.5190550606236569E-2</v>
+        <v>4.5966933173947448E-2</v>
       </c>
       <c r="D56" t="s">
         <v>67</v>
@@ -5741,7 +5380,7 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
@@ -5770,13 +5409,13 @@
         <v>70</v>
       </c>
       <c r="B2">
-        <v>2530.4238</v>
+        <v>1878.7887000000001</v>
       </c>
       <c r="C2">
-        <v>6029.2999999999993</v>
+        <v>6249.7</v>
       </c>
       <c r="D2">
-        <v>29884.121794999999</v>
+        <v>22478.798005000001</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
@@ -5790,13 +5429,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="82" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5810,26 +5448,26 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
       <c r="B2">
-        <v>478.91</v>
+        <v>2500</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
       <c r="B3">
-        <v>2991.84</v>
+        <v>719</v>
       </c>
       <c r="C3" t="s">
-        <v>217</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5837,10 +5475,10 @@
         <v>74</v>
       </c>
       <c r="B4">
-        <v>5010.87</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5848,189 +5486,189 @@
         <v>75</v>
       </c>
       <c r="B5">
-        <v>1444.22</v>
+        <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>76</v>
       </c>
       <c r="B6">
-        <v>194.52</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>77</v>
       </c>
       <c r="B7">
-        <v>1354.89</v>
+        <v>311</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8">
-        <v>904.36999999999989</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>79</v>
       </c>
       <c r="B9">
-        <v>549.11000000000013</v>
+        <v>485</v>
       </c>
       <c r="C9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>80</v>
       </c>
       <c r="B10">
-        <v>1345.57</v>
+        <v>2150</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>81</v>
       </c>
       <c r="B11">
-        <v>647.38</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>82</v>
       </c>
       <c r="B12">
-        <v>90.579999999999984</v>
+        <v>1486</v>
       </c>
       <c r="C12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>83</v>
       </c>
       <c r="B13">
-        <v>833.9</v>
+        <v>1692.57</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>84</v>
       </c>
       <c r="B14">
-        <v>602.4</v>
+        <v>280</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>85</v>
       </c>
       <c r="B15">
-        <v>3344.2199999999989</v>
+        <v>787</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
       <c r="B16">
-        <v>1321.02</v>
+        <v>1450</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
       <c r="B17">
-        <v>181.54</v>
+        <v>2500</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>88</v>
       </c>
       <c r="B18">
-        <v>903.18999999999994</v>
+        <v>679</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
       <c r="B19">
-        <v>4259.84</v>
+        <v>1250</v>
       </c>
       <c r="C19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>90</v>
       </c>
       <c r="B20">
-        <v>2971.83</v>
+        <v>1850</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>91</v>
       </c>
       <c r="B21">
-        <v>635.02</v>
+        <v>963</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -6038,1428 +5676,66 @@
         <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>93</v>
       </c>
       <c r="B23">
-        <v>150</v>
+        <v>1040</v>
       </c>
       <c r="C23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>94</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>95</v>
       </c>
       <c r="B25">
-        <v>420</v>
+        <v>887</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>96</v>
       </c>
       <c r="B26">
-        <v>105.18</v>
+        <v>2500</v>
       </c>
       <c r="C26" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>97</v>
       </c>
       <c r="B27">
-        <v>275.3</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
         <v>98</v>
       </c>
-      <c r="B28">
-        <v>97.06</v>
-      </c>
-      <c r="C28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29">
-        <v>366.44</v>
-      </c>
-      <c r="C29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30">
-        <v>93.52</v>
-      </c>
-      <c r="C30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31">
-        <v>459.54</v>
-      </c>
-      <c r="C31" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32">
-        <v>2450.0100000000002</v>
-      </c>
-      <c r="C32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33">
-        <v>185.32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34">
-        <v>1504.33</v>
-      </c>
-      <c r="C34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35">
-        <v>1231.01</v>
-      </c>
-      <c r="C35" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36">
-        <v>1005.85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37">
-        <v>1714.26</v>
-      </c>
-      <c r="C37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38">
-        <v>10520.54</v>
-      </c>
-      <c r="C38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>109</v>
-      </c>
-      <c r="B39">
-        <v>11506.65</v>
-      </c>
-      <c r="C39" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40">
-        <v>9312.6999999999989</v>
-      </c>
-      <c r="C40" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>111</v>
-      </c>
-      <c r="B41">
-        <v>1219.25</v>
-      </c>
-      <c r="C41" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42">
-        <v>11606.83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43">
-        <v>11426.54</v>
-      </c>
-      <c r="C43" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44">
-        <v>12825.35</v>
-      </c>
-      <c r="C44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45">
-        <v>2902.85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46">
-        <v>11016.17</v>
-      </c>
-      <c r="C46" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B47">
-        <v>2663.36</v>
-      </c>
-      <c r="C47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48">
-        <v>7244.7800000000007</v>
-      </c>
-      <c r="C48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B49">
-        <v>9545.66</v>
-      </c>
-      <c r="C49" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>120</v>
-      </c>
-      <c r="B50">
-        <v>26427.48</v>
-      </c>
-      <c r="C50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>121</v>
-      </c>
-      <c r="B51">
-        <v>3459.34</v>
-      </c>
-      <c r="C51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52">
-        <v>25405.58</v>
-      </c>
-      <c r="C52" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>123</v>
-      </c>
-      <c r="B53">
-        <v>5945.52</v>
-      </c>
-      <c r="C53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54">
-        <v>24410.66</v>
-      </c>
-      <c r="C54" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55">
-        <v>20124.27</v>
-      </c>
-      <c r="C55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56">
-        <v>17465.84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>127</v>
-      </c>
-      <c r="B57">
-        <v>11428.65</v>
-      </c>
-      <c r="C57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>128</v>
-      </c>
-      <c r="B58">
-        <v>8575.7699999999986</v>
-      </c>
-      <c r="C58" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>129</v>
-      </c>
-      <c r="B59">
-        <v>15242.37</v>
-      </c>
-      <c r="C59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60">
-        <v>24034.11</v>
-      </c>
-      <c r="C60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61">
-        <v>28537.63</v>
-      </c>
-      <c r="C61" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>132</v>
-      </c>
-      <c r="B62">
-        <v>30254.12</v>
-      </c>
-      <c r="C62" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>133</v>
-      </c>
-      <c r="B63">
-        <v>9818.52</v>
-      </c>
-      <c r="C63" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64">
-        <v>4825.04</v>
-      </c>
-      <c r="C64" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>135</v>
-      </c>
-      <c r="B65">
-        <v>1205.78</v>
-      </c>
-      <c r="C65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66">
-        <v>280.72000000000003</v>
-      </c>
-      <c r="C66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>137</v>
-      </c>
-      <c r="B67">
-        <v>49.14</v>
-      </c>
-      <c r="C67" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68">
-        <v>2196.4899999999998</v>
-      </c>
-      <c r="C68" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>139</v>
-      </c>
-      <c r="B69">
-        <v>1425.81</v>
-      </c>
-      <c r="C69" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70">
-        <v>2000.9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>141</v>
-      </c>
-      <c r="B71">
-        <v>200</v>
-      </c>
-      <c r="C71" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72">
-        <v>20</v>
-      </c>
-      <c r="C72" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>143</v>
-      </c>
-      <c r="B73">
-        <v>19295.38</v>
-      </c>
-      <c r="C73" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>144</v>
-      </c>
-      <c r="B74">
-        <v>8862.619999999999</v>
-      </c>
-      <c r="C74" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75">
-        <v>25644.43</v>
-      </c>
-      <c r="C75" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>146</v>
-      </c>
-      <c r="B76">
-        <v>1310.69</v>
-      </c>
-      <c r="C76" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>147</v>
-      </c>
-      <c r="B77">
-        <v>503.15</v>
-      </c>
-      <c r="C77" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78">
-        <v>143.19999999999999</v>
-      </c>
-      <c r="C78" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>149</v>
-      </c>
-      <c r="B79">
-        <v>887.19</v>
-      </c>
-      <c r="C79" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>150</v>
-      </c>
-      <c r="B80">
-        <v>627.17000000000007</v>
-      </c>
-      <c r="C80" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>151</v>
-      </c>
-      <c r="B81">
-        <v>1778.96</v>
-      </c>
-      <c r="C81" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82">
-        <v>2087.25</v>
-      </c>
-      <c r="C82" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>153</v>
-      </c>
-      <c r="B83">
-        <v>305.38</v>
-      </c>
-      <c r="C83" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84">
-        <v>982.07999999999993</v>
-      </c>
-      <c r="C84" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>155</v>
-      </c>
-      <c r="B85">
-        <v>4308.8900000000003</v>
-      </c>
-      <c r="C85" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86">
-        <v>564.79999999999995</v>
-      </c>
-      <c r="C86" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>157</v>
-      </c>
-      <c r="B87">
-        <v>1048.8</v>
-      </c>
-      <c r="C87" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>158</v>
-      </c>
-      <c r="B88">
-        <v>2982.12</v>
-      </c>
-      <c r="C88" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>159</v>
-      </c>
-      <c r="B89">
-        <v>282.13</v>
-      </c>
-      <c r="C89" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>160</v>
-      </c>
-      <c r="B90">
-        <v>3707.68</v>
-      </c>
-      <c r="C90" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>161</v>
-      </c>
-      <c r="B91">
-        <v>2506.59</v>
-      </c>
-      <c r="C91" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>162</v>
-      </c>
-      <c r="B92">
-        <v>1361.56</v>
-      </c>
-      <c r="C92" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>163</v>
-      </c>
-      <c r="B93">
-        <v>3390.440000000001</v>
-      </c>
-      <c r="C93" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>164</v>
-      </c>
-      <c r="B94">
-        <v>566.69000000000005</v>
-      </c>
-      <c r="C94" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>165</v>
-      </c>
-      <c r="B95">
-        <v>1579.08</v>
-      </c>
-      <c r="C95" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>166</v>
-      </c>
-      <c r="B96">
-        <v>2907.12</v>
-      </c>
-      <c r="C96" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>167</v>
-      </c>
-      <c r="B97">
-        <v>5017.21</v>
-      </c>
-      <c r="C97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>168</v>
-      </c>
-      <c r="B98">
-        <v>1930.08</v>
-      </c>
-      <c r="C98" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>169</v>
-      </c>
-      <c r="B99">
-        <v>5007.6499999999996</v>
-      </c>
-      <c r="C99" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>170</v>
-      </c>
-      <c r="B100">
-        <v>70</v>
-      </c>
-      <c r="C100" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>171</v>
-      </c>
-      <c r="B101">
-        <v>567.19000000000005</v>
-      </c>
-      <c r="C101" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>172</v>
-      </c>
-      <c r="B102">
-        <v>25201.27</v>
-      </c>
-      <c r="C102" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>173</v>
-      </c>
-      <c r="B103">
-        <v>8358.14</v>
-      </c>
-      <c r="C103" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>174</v>
-      </c>
-      <c r="B104">
-        <v>425.12</v>
-      </c>
-      <c r="C104" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>175</v>
-      </c>
-      <c r="B105">
-        <v>2829.33</v>
-      </c>
-      <c r="C105" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>176</v>
-      </c>
-      <c r="B106">
-        <v>386.01</v>
-      </c>
-      <c r="C106" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>177</v>
-      </c>
-      <c r="B107">
-        <v>604.9</v>
-      </c>
-      <c r="C107" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>178</v>
-      </c>
-      <c r="B108">
-        <v>3504.32</v>
-      </c>
-      <c r="C108" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>179</v>
-      </c>
-      <c r="B109">
-        <v>668.5</v>
-      </c>
-      <c r="C109" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>180</v>
-      </c>
-      <c r="B110">
-        <v>717.56</v>
-      </c>
-      <c r="C110" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>181</v>
-      </c>
-      <c r="B111">
-        <v>658.26</v>
-      </c>
-      <c r="C111" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>182</v>
-      </c>
-      <c r="B112">
-        <v>1355.8</v>
-      </c>
-      <c r="C112" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>183</v>
-      </c>
-      <c r="B113">
-        <v>3143.71</v>
-      </c>
-      <c r="C113" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>184</v>
-      </c>
-      <c r="B114">
-        <v>1598.24</v>
-      </c>
-      <c r="C114" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>185</v>
-      </c>
-      <c r="B115">
-        <v>2839.64</v>
-      </c>
-      <c r="C115" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>186</v>
-      </c>
-      <c r="B116">
-        <v>1408.5</v>
-      </c>
-      <c r="C116" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>187</v>
-      </c>
-      <c r="B117">
-        <v>2591.4899999999998</v>
-      </c>
-      <c r="C117" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>188</v>
-      </c>
-      <c r="B118">
-        <v>1008.78</v>
-      </c>
-      <c r="C118" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>189</v>
-      </c>
-      <c r="B119">
-        <v>3269.86</v>
-      </c>
-      <c r="C119" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>190</v>
-      </c>
-      <c r="B120">
-        <v>17290.98</v>
-      </c>
-      <c r="C120" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>191</v>
-      </c>
-      <c r="B121">
-        <v>19155.28</v>
-      </c>
-      <c r="C121" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>192</v>
-      </c>
-      <c r="B122">
-        <v>14870.68</v>
-      </c>
-      <c r="C122" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>193</v>
-      </c>
-      <c r="B123">
-        <v>1934.52</v>
-      </c>
-      <c r="C123" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>194</v>
-      </c>
-      <c r="B124">
-        <v>273.79000000000002</v>
-      </c>
-      <c r="C124" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>195</v>
-      </c>
-      <c r="B125">
-        <v>12976.36</v>
-      </c>
-      <c r="C125" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>196</v>
-      </c>
-      <c r="B126">
-        <v>4217.58</v>
-      </c>
-      <c r="C126" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>197</v>
-      </c>
-      <c r="B127">
-        <v>2173.56</v>
-      </c>
-      <c r="C127" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>198</v>
-      </c>
-      <c r="B128">
-        <v>534.5</v>
-      </c>
-      <c r="C128" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>199</v>
-      </c>
-      <c r="B129">
-        <v>6211.369999999999</v>
-      </c>
-      <c r="C129" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>200</v>
-      </c>
-      <c r="B130">
-        <v>8730.7200000000012</v>
-      </c>
-      <c r="C130" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>201</v>
-      </c>
-      <c r="B131">
-        <v>3956.61</v>
-      </c>
-      <c r="C131" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>202</v>
-      </c>
-      <c r="B132">
-        <v>124.86</v>
-      </c>
-      <c r="C132" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>203</v>
-      </c>
-      <c r="B133">
-        <v>13467.77</v>
-      </c>
-      <c r="C133" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>204</v>
-      </c>
-      <c r="B134">
-        <v>8396.2099999999991</v>
-      </c>
-      <c r="C134" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>205</v>
-      </c>
-      <c r="B135">
-        <v>5225.9699999999993</v>
-      </c>
-      <c r="C135" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>206</v>
-      </c>
-      <c r="B136">
-        <v>4250.7199999999993</v>
-      </c>
-      <c r="C136" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>207</v>
-      </c>
-      <c r="B137">
-        <v>503.15</v>
-      </c>
-      <c r="C137" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>208</v>
-      </c>
-      <c r="B138">
-        <v>1780.05</v>
-      </c>
-      <c r="C138" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>209</v>
-      </c>
-      <c r="B139">
-        <v>1578.92</v>
-      </c>
-      <c r="C139" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>210</v>
-      </c>
-      <c r="B140">
-        <v>295.89999999999998</v>
-      </c>
-      <c r="C140" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>211</v>
-      </c>
-      <c r="B141">
-        <v>1708.09</v>
-      </c>
-      <c r="C141" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>212</v>
-      </c>
-      <c r="B142">
-        <v>4336.76</v>
-      </c>
-      <c r="C142" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>213</v>
-      </c>
-      <c r="B143">
-        <v>1883.65</v>
-      </c>
-      <c r="C143" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>214</v>
-      </c>
-      <c r="B144">
-        <v>1590.07</v>
-      </c>
-      <c r="C144" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>215</v>
-      </c>
-      <c r="B145">
-        <v>1664.88</v>
-      </c>
-      <c r="C145" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>216</v>
-      </c>
-      <c r="B146">
-        <v>3820.53</v>
-      </c>
-      <c r="C146" t="s">
-        <v>217</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C146" xr:uid="{00000000-0001-0000-0400-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="B 9225 BL"/>
-        <filter val="B 9273 NK"/>
-        <filter val="L 8073 UL (EX.L 8341 UR)"/>
-        <filter val="L 8251 UO"/>
-        <filter val="L 8408 UO"/>
-        <filter val="L 8487 UK (EX.L 9631 US)"/>
-        <filter val="L 8595 UK (EX.L 9624 US)"/>
-        <filter val="L 8604 UK (EX.L 9620 US)"/>
-        <filter val="L 8609 UT ( EX L 7954 MU )"/>
-        <filter val="L 8613 UK (EX.L 9566 UQ)"/>
-        <filter val="L 8622 UK (EX.L 9626 US)"/>
-        <filter val="L 8625 US"/>
-        <filter val="L 8625 UT"/>
-        <filter val="L 8631 UK (EX.L 9623 US)"/>
-        <filter val="L 8658 UK (EX.L 9582 UQ)"/>
-        <filter val="L 8676 UK (EX.L 9581 UQ)"/>
-        <filter val="L 8703 UK (EX.L 9173 UQ)"/>
-        <filter val="L 8796 UO (EX.L 9025 US)"/>
-        <filter val="L 9049 UQ"/>
-        <filter val="L 9049 US"/>
-        <filter val="L 9061 UR"/>
-        <filter val="L 9098 UA (EX.L 9690 UO)"/>
-        <filter val="L 9622 US"/>
-        <filter val="L 9633 US"/>
-        <filter val="L 9743 UR"/>
-        <filter val="L 9968 CQ (EX.L 8084 NQ)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:C27" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>